--- a/calificaciones.xlsx
+++ b/calificaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicalc\Documents\UPB\Calificaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1A931B-4072-473E-B7DB-2E36F0907ADD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EA2BC2-A4D5-4BB8-AF7A-368EF272992B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="240">
   <si>
     <t>matricula</t>
   </si>
@@ -418,6 +418,333 @@
   </si>
   <si>
     <t>promedio</t>
+  </si>
+  <si>
+    <t>CORONA MALDONADO JUAN RAFAEL</t>
+  </si>
+  <si>
+    <t>ERNÁNDEZ CASTRO MEREDITH VIENEY</t>
+  </si>
+  <si>
+    <t>GONZALEZ GUERRERO DANIELA</t>
+  </si>
+  <si>
+    <t>Gonzalez Rodriguez Vanesa Geraldine</t>
+  </si>
+  <si>
+    <t>GRAJEDA VARGAS EINAR ISRAEL</t>
+  </si>
+  <si>
+    <t>Juarez Morquecho Javier Antonio</t>
+  </si>
+  <si>
+    <t>Lopez Mendez Ximena Montserrat</t>
+  </si>
+  <si>
+    <t>MARTÍNEZ CAUDILLO MATTHEW IOSHUA</t>
+  </si>
+  <si>
+    <t>Martínez Ortega Paloma Jimena</t>
+  </si>
+  <si>
+    <t>Mendiola Guevara Alexis Misael</t>
+  </si>
+  <si>
+    <t>Olmedo Santana Diego</t>
+  </si>
+  <si>
+    <t>PEREZ DE ALBA LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>PÉREZ SORIA PAOLA JAZMÍN</t>
+  </si>
+  <si>
+    <t>QUINTERO IBARRA ABRIL ITZEL</t>
+  </si>
+  <si>
+    <t>Ramirez Martínez Brayan</t>
+  </si>
+  <si>
+    <t>RAMOS VITAL ANDRÉS</t>
+  </si>
+  <si>
+    <t>RANGEL HERNÁNDEZ ARIEL ANTONIO</t>
+  </si>
+  <si>
+    <t>REMIGIO GARCIA LEOPOLDO</t>
+  </si>
+  <si>
+    <t>ROMERO AGUILAR CHRISTIAN URIEL</t>
+  </si>
+  <si>
+    <t>Romero Meza Gema Jhoana</t>
+  </si>
+  <si>
+    <t>SÁNCHEZ SÁNCHEZ ARANZA SARAHI</t>
+  </si>
+  <si>
+    <t>SOLIS ORTEGA GABRIELA VANESSA</t>
+  </si>
+  <si>
+    <t>TORRES CASTILLO JOSÉ MARTIN</t>
+  </si>
+  <si>
+    <t>VARGAS RENDÓN LUZ OFELIA</t>
+  </si>
+  <si>
+    <t>Vazquez Hernandez Andrea Guadalupe</t>
+  </si>
+  <si>
+    <t>Sep-Dic</t>
+  </si>
+  <si>
+    <t>TDLI</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>ARREDONDO BELTRÁN GUSTAVO ALFONSO</t>
+  </si>
+  <si>
+    <t>PADILLA LUNA ANGEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>PÉREZ VELÁZQUEZ ERNESTO</t>
+  </si>
+  <si>
+    <t>RAMIREZ MORENO ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>SALAZAR INFANTE SUSAN GABRIEL</t>
+  </si>
+  <si>
+    <t>YEBRA SANDOVAL MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>FAPI</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>FERNÁNDEZ CASTRO MEREDITH VIENEY</t>
+  </si>
+  <si>
+    <t>GONZÁLEZ GUERRERO DANIELA</t>
+  </si>
+  <si>
+    <t>Grajeda Vargas Einar Israel</t>
+  </si>
+  <si>
+    <t>Juárez Morquecho Javier Antonio</t>
+  </si>
+  <si>
+    <t>Pérez de Alba Luis Angel</t>
+  </si>
+  <si>
+    <t>VARGAS RENDON LUZ OFELIA</t>
+  </si>
+  <si>
+    <t>IDM</t>
+  </si>
+  <si>
+    <t>AGUILAR MALDONADO JOSÉ EMMANUEL</t>
+  </si>
+  <si>
+    <t>AGUILAR MEJÍA MELISSA</t>
+  </si>
+  <si>
+    <t>ALONSO SALAZAR RICARDO ISAI</t>
+  </si>
+  <si>
+    <t>CHÁVEZ HERNÁNDEZ JUAN PABLO</t>
+  </si>
+  <si>
+    <t>GUZMÁN NEGRETE KAMILA YURIDIA</t>
+  </si>
+  <si>
+    <t>HERNÁNDEZ HERNÁNDEZ JORGE ALBERTO</t>
+  </si>
+  <si>
+    <t>LOPEZ CAMPOS FABIAN JOEL</t>
+  </si>
+  <si>
+    <t>MACIEL HERNANDEZ KAREN JOCELYN</t>
+  </si>
+  <si>
+    <t>MARTÍNEZ TAPIA KENNETH WENDOLYNE</t>
+  </si>
+  <si>
+    <t>MEDEL MOSQUEDA PABLO LEONARDO</t>
+  </si>
+  <si>
+    <t>Morales Díaz Alan David</t>
+  </si>
+  <si>
+    <t>MORENO NAVARRO JORGE DANIEL</t>
+  </si>
+  <si>
+    <t>PADILLA FUENTES CARLOS MAURICIO</t>
+  </si>
+  <si>
+    <t>PÉREZ AVALOS LEONARDO DANIEL</t>
+  </si>
+  <si>
+    <t>RODRÍGUEZ GARCIA MAYTEE SARAI</t>
+  </si>
+  <si>
+    <t>RODRÍGUEZ GÓMEZ JOSÉ EZEQUIEL</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ SOTOMAYOR JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>ROQUE GARCÍA ALEXA CANDELARIA</t>
+  </si>
+  <si>
+    <t>SALDIVAR CAUDILLO ULISES GUADALUPE</t>
+  </si>
+  <si>
+    <t>SANTIAGO ALCANTAR ARLETTE LIZETH</t>
+  </si>
+  <si>
+    <t>Silva Elias Brandon Jhoan</t>
+  </si>
+  <si>
+    <t>SIMENTAL RODRÍGUEZ DIANA</t>
+  </si>
+  <si>
+    <t>TORRES RODRIGUEZ KEVIN JOSUÉ</t>
+  </si>
+  <si>
+    <t>4C</t>
+  </si>
+  <si>
+    <t>YEBRA SANDOVAL MARÍA GUADALUPE</t>
+  </si>
+  <si>
+    <t>RAMIREZ MORENO ÁNGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>PADILLA LUNA ÁNGEL ENRIQUE</t>
+  </si>
+  <si>
+    <t>MONROY GUEVARA MARÍA GUADALUPE</t>
+  </si>
+  <si>
+    <t>PEREZ VERA LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>ALONSO SALAZAR RICARDO ISAÍ</t>
+  </si>
+  <si>
+    <t>NAVARRO TETUÁN ÁGEL RICARDO</t>
+  </si>
+  <si>
+    <t>Ene-Abr</t>
+  </si>
+  <si>
+    <t>CVV</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>AGUAYO CHAVEZ JONATHAN DE JESÚS</t>
+  </si>
+  <si>
+    <t>AGUIRRE HERNANDEZ EDGAR OMAR</t>
+  </si>
+  <si>
+    <t>ÁLVAREZ MANRÍQUEZ DARIANN LEILANI</t>
+  </si>
+  <si>
+    <t>BONILLA AYALA RAYMUNDO</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA BONILLA JESUS EDUARDO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA MUÑOZ MIRANDA</t>
+  </si>
+  <si>
+    <t>GÓMEZ MORENO OTILIO EMMANUEL</t>
+  </si>
+  <si>
+    <t>GÓMEZ RODRÍGUEZ CRISTINA</t>
+  </si>
+  <si>
+    <t>HERNÁNDEZ ORTEGA CLARA YESENIA</t>
+  </si>
+  <si>
+    <t>HUERTA CAUDILLO LUIS ERNESTO</t>
+  </si>
+  <si>
+    <t>LEON AGUILAR OLIVER ANTONIO</t>
+  </si>
+  <si>
+    <t>MALDONADO CASTRO WENDY CAROLINA</t>
+  </si>
+  <si>
+    <t>MENDIOLA NATAL KEVIN ALONSO</t>
+  </si>
+  <si>
+    <t>MORALES CAUDILLO SAUL ALBERTO</t>
+  </si>
+  <si>
+    <t>MUÑIZ AYALA ANTHONY ALEXANDER</t>
+  </si>
+  <si>
+    <t>NIEVES RODRÍGUEZ ERICK DANIEL</t>
+  </si>
+  <si>
+    <t>PATLÁN LOZANO PAULINA IVETTE</t>
+  </si>
+  <si>
+    <t>PEÑUELAS MENDEZ DANIELA</t>
+  </si>
+  <si>
+    <t>PONCE HERNÁNDEZ OSCAR DAVID</t>
+  </si>
+  <si>
+    <t>RAMÍREZ HERNÁNDEZ CAMILA</t>
+  </si>
+  <si>
+    <t>RAMÍREZ RODRÍGUEZ ERIKA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ROCHA BALANDRÁN ERANDY MARLENNE</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ REA NANCY ESMERALDA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ REYNOSO JESUS EDUARDO</t>
+  </si>
+  <si>
+    <t>RODRÍGUEZ RODRÍGUEZ JUSTIN ISRAEL</t>
+  </si>
+  <si>
+    <t>RODRÍGUEZ VÁZQUEZ BRYAN ALEXIS</t>
+  </si>
+  <si>
+    <t>VALADEZ ORTEGA FRANCISCO EMILIANO</t>
+  </si>
+  <si>
+    <t>VÁZQUEZ GONZÁLEZ ESTEFANY</t>
+  </si>
+  <si>
+    <t>VEGA CONTRERAS JORGE ENRIQUE</t>
+  </si>
+  <si>
+    <t>VELÁZQUEZ CUÉLLAR JARET ALESSANDRO</t>
+  </si>
+  <si>
+    <t>VILLANUEVA FLORES JUAN DE DIOS</t>
+  </si>
+  <si>
+    <t>EDI</t>
   </si>
 </sst>
 </file>
@@ -461,10 +788,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="1"/>
@@ -3690,14 +4023,14 @@
         <v>8.5258076923076906</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" ref="M67:M101" si="2">AVERAGE(H67:L67)</f>
+        <f t="shared" ref="M67:M130" si="2">AVERAGE(H67:L67)</f>
         <v>8.2488165445665445</v>
       </c>
       <c r="N67">
         <v>6</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" ref="Q67:Q101" si="3">MAX(M67,O67,P67)</f>
+        <f t="shared" ref="Q67:Q130" si="3">MAX(M67,O67,P67)</f>
         <v>8.2488165445665445</v>
       </c>
     </row>
@@ -5062,6 +5395,5471 @@
       <c r="Q101" s="1">
         <f t="shared" si="3"/>
         <v>10.01359375</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>24033441</v>
+      </c>
+      <c r="B102" t="s">
+        <v>131</v>
+      </c>
+      <c r="C102" t="s">
+        <v>27</v>
+      </c>
+      <c r="D102">
+        <v>2025</v>
+      </c>
+      <c r="E102" t="s">
+        <v>156</v>
+      </c>
+      <c r="F102" t="s">
+        <v>157</v>
+      </c>
+      <c r="G102" t="s">
+        <v>158</v>
+      </c>
+      <c r="H102">
+        <v>7.2</v>
+      </c>
+      <c r="I102">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J102">
+        <v>10</v>
+      </c>
+      <c r="M102" s="1">
+        <f t="shared" si="2"/>
+        <v>8.4666666666666668</v>
+      </c>
+      <c r="Q102" s="1">
+        <f t="shared" si="3"/>
+        <v>8.4666666666666668</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>24033586</v>
+      </c>
+      <c r="B103" t="s">
+        <v>132</v>
+      </c>
+      <c r="C103" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103">
+        <v>2025</v>
+      </c>
+      <c r="E103" t="s">
+        <v>156</v>
+      </c>
+      <c r="F103" t="s">
+        <v>157</v>
+      </c>
+      <c r="G103" t="s">
+        <v>158</v>
+      </c>
+      <c r="H103">
+        <v>10</v>
+      </c>
+      <c r="I103">
+        <v>10</v>
+      </c>
+      <c r="J103">
+        <v>10</v>
+      </c>
+      <c r="M103" s="1">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="Q103" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>24033161</v>
+      </c>
+      <c r="B104" t="s">
+        <v>133</v>
+      </c>
+      <c r="C104" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104">
+        <v>2025</v>
+      </c>
+      <c r="E104" t="s">
+        <v>156</v>
+      </c>
+      <c r="F104" t="s">
+        <v>157</v>
+      </c>
+      <c r="G104" t="s">
+        <v>158</v>
+      </c>
+      <c r="H104">
+        <v>7.0333333333333332</v>
+      </c>
+      <c r="I104">
+        <v>9.879999999999999</v>
+      </c>
+      <c r="J104">
+        <v>10</v>
+      </c>
+      <c r="M104" s="1">
+        <f t="shared" si="2"/>
+        <v>8.9711111111111119</v>
+      </c>
+      <c r="Q104" s="1">
+        <f t="shared" si="3"/>
+        <v>8.9711111111111119</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>24033450</v>
+      </c>
+      <c r="B105" t="s">
+        <v>134</v>
+      </c>
+      <c r="C105" t="s">
+        <v>28</v>
+      </c>
+      <c r="D105">
+        <v>2025</v>
+      </c>
+      <c r="E105" t="s">
+        <v>156</v>
+      </c>
+      <c r="F105" t="s">
+        <v>157</v>
+      </c>
+      <c r="G105" t="s">
+        <v>158</v>
+      </c>
+      <c r="H105">
+        <v>8.5</v>
+      </c>
+      <c r="I105">
+        <v>9.58</v>
+      </c>
+      <c r="J105">
+        <v>10</v>
+      </c>
+      <c r="M105" s="1">
+        <f t="shared" si="2"/>
+        <v>9.36</v>
+      </c>
+      <c r="Q105" s="1">
+        <f t="shared" si="3"/>
+        <v>9.36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>24033384</v>
+      </c>
+      <c r="B106" t="s">
+        <v>135</v>
+      </c>
+      <c r="C106" t="s">
+        <v>27</v>
+      </c>
+      <c r="D106">
+        <v>2025</v>
+      </c>
+      <c r="E106" t="s">
+        <v>156</v>
+      </c>
+      <c r="F106" t="s">
+        <v>157</v>
+      </c>
+      <c r="G106" t="s">
+        <v>158</v>
+      </c>
+      <c r="H106">
+        <v>4.9666666666666668</v>
+      </c>
+      <c r="I106">
+        <v>8.046153846153846</v>
+      </c>
+      <c r="J106">
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="M106" s="1">
+        <f t="shared" si="2"/>
+        <v>4.5598290598290596</v>
+      </c>
+      <c r="Q106" s="1">
+        <f t="shared" si="3"/>
+        <v>4.5598290598290596</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>24033611</v>
+      </c>
+      <c r="B107" t="s">
+        <v>136</v>
+      </c>
+      <c r="C107" t="s">
+        <v>27</v>
+      </c>
+      <c r="D107">
+        <v>2025</v>
+      </c>
+      <c r="E107" t="s">
+        <v>156</v>
+      </c>
+      <c r="F107" t="s">
+        <v>157</v>
+      </c>
+      <c r="G107" t="s">
+        <v>158</v>
+      </c>
+      <c r="H107">
+        <v>7.3666666666666671</v>
+      </c>
+      <c r="I107">
+        <v>9.5384615384615383</v>
+      </c>
+      <c r="J107">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M107" s="1">
+        <f t="shared" si="2"/>
+        <v>8.7461538461538471</v>
+      </c>
+      <c r="Q107" s="1">
+        <f t="shared" si="3"/>
+        <v>8.7461538461538471</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>24033129</v>
+      </c>
+      <c r="B108" t="s">
+        <v>137</v>
+      </c>
+      <c r="C108" t="s">
+        <v>28</v>
+      </c>
+      <c r="D108">
+        <v>2025</v>
+      </c>
+      <c r="E108" t="s">
+        <v>156</v>
+      </c>
+      <c r="F108" t="s">
+        <v>157</v>
+      </c>
+      <c r="G108" t="s">
+        <v>158</v>
+      </c>
+      <c r="H108">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I108">
+        <v>10</v>
+      </c>
+      <c r="J108">
+        <v>10</v>
+      </c>
+      <c r="M108" s="1">
+        <f t="shared" si="2"/>
+        <v>9.5666666666666664</v>
+      </c>
+      <c r="Q108" s="1">
+        <f t="shared" si="3"/>
+        <v>9.5666666666666664</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>24033036</v>
+      </c>
+      <c r="B109" t="s">
+        <v>138</v>
+      </c>
+      <c r="C109" t="s">
+        <v>27</v>
+      </c>
+      <c r="D109">
+        <v>2025</v>
+      </c>
+      <c r="E109" t="s">
+        <v>156</v>
+      </c>
+      <c r="F109" t="s">
+        <v>157</v>
+      </c>
+      <c r="G109" t="s">
+        <v>158</v>
+      </c>
+      <c r="H109">
+        <v>10</v>
+      </c>
+      <c r="I109">
+        <v>9.879999999999999</v>
+      </c>
+      <c r="J109">
+        <v>10</v>
+      </c>
+      <c r="M109" s="1">
+        <f t="shared" si="2"/>
+        <v>9.9599999999999991</v>
+      </c>
+      <c r="Q109" s="1">
+        <f t="shared" si="3"/>
+        <v>9.9599999999999991</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>24033306</v>
+      </c>
+      <c r="B110" t="s">
+        <v>139</v>
+      </c>
+      <c r="C110" t="s">
+        <v>28</v>
+      </c>
+      <c r="D110">
+        <v>2025</v>
+      </c>
+      <c r="E110" t="s">
+        <v>156</v>
+      </c>
+      <c r="F110" t="s">
+        <v>157</v>
+      </c>
+      <c r="G110" t="s">
+        <v>158</v>
+      </c>
+      <c r="H110">
+        <v>7.8</v>
+      </c>
+      <c r="I110">
+        <v>9.195384615384615</v>
+      </c>
+      <c r="J110">
+        <v>10</v>
+      </c>
+      <c r="M110" s="1">
+        <f t="shared" si="2"/>
+        <v>8.9984615384615392</v>
+      </c>
+      <c r="Q110" s="1">
+        <f t="shared" si="3"/>
+        <v>8.9984615384615392</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>24033244</v>
+      </c>
+      <c r="B111" t="s">
+        <v>140</v>
+      </c>
+      <c r="C111" t="s">
+        <v>27</v>
+      </c>
+      <c r="D111">
+        <v>2025</v>
+      </c>
+      <c r="E111" t="s">
+        <v>156</v>
+      </c>
+      <c r="F111" t="s">
+        <v>157</v>
+      </c>
+      <c r="G111" t="s">
+        <v>158</v>
+      </c>
+      <c r="H111">
+        <v>7.8</v>
+      </c>
+      <c r="I111">
+        <v>10</v>
+      </c>
+      <c r="J111">
+        <v>8</v>
+      </c>
+      <c r="M111" s="1">
+        <f t="shared" si="2"/>
+        <v>8.6</v>
+      </c>
+      <c r="Q111" s="1">
+        <f t="shared" si="3"/>
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>24033460</v>
+      </c>
+      <c r="B112" t="s">
+        <v>141</v>
+      </c>
+      <c r="C112" t="s">
+        <v>27</v>
+      </c>
+      <c r="D112">
+        <v>2025</v>
+      </c>
+      <c r="E112" t="s">
+        <v>156</v>
+      </c>
+      <c r="F112" t="s">
+        <v>157</v>
+      </c>
+      <c r="G112" t="s">
+        <v>158</v>
+      </c>
+      <c r="H112">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I112">
+        <v>10</v>
+      </c>
+      <c r="J112">
+        <v>10</v>
+      </c>
+      <c r="M112" s="1">
+        <f t="shared" si="2"/>
+        <v>9.7666666666666675</v>
+      </c>
+      <c r="Q112" s="1">
+        <f t="shared" si="3"/>
+        <v>9.7666666666666675</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>24033435</v>
+      </c>
+      <c r="B113" t="s">
+        <v>142</v>
+      </c>
+      <c r="C113" t="s">
+        <v>27</v>
+      </c>
+      <c r="D113">
+        <v>2025</v>
+      </c>
+      <c r="E113" t="s">
+        <v>156</v>
+      </c>
+      <c r="F113" t="s">
+        <v>157</v>
+      </c>
+      <c r="G113" t="s">
+        <v>158</v>
+      </c>
+      <c r="H113">
+        <v>8</v>
+      </c>
+      <c r="I113">
+        <v>9.6461538461538456</v>
+      </c>
+      <c r="J113">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="M113" s="1">
+        <f t="shared" si="2"/>
+        <v>8.77094017094017</v>
+      </c>
+      <c r="Q113" s="1">
+        <f t="shared" si="3"/>
+        <v>8.77094017094017</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>24033330</v>
+      </c>
+      <c r="B114" t="s">
+        <v>143</v>
+      </c>
+      <c r="C114" t="s">
+        <v>28</v>
+      </c>
+      <c r="D114">
+        <v>2025</v>
+      </c>
+      <c r="E114" t="s">
+        <v>156</v>
+      </c>
+      <c r="F114" t="s">
+        <v>157</v>
+      </c>
+      <c r="G114" t="s">
+        <v>158</v>
+      </c>
+      <c r="H114">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I114">
+        <v>9.4461538461538463</v>
+      </c>
+      <c r="J114">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M114" s="1">
+        <f t="shared" si="2"/>
+        <v>9.3264957264957271</v>
+      </c>
+      <c r="Q114" s="1">
+        <f t="shared" si="3"/>
+        <v>9.3264957264957271</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>24032968</v>
+      </c>
+      <c r="B115" t="s">
+        <v>144</v>
+      </c>
+      <c r="C115" t="s">
+        <v>28</v>
+      </c>
+      <c r="D115">
+        <v>2025</v>
+      </c>
+      <c r="E115" t="s">
+        <v>156</v>
+      </c>
+      <c r="F115" t="s">
+        <v>157</v>
+      </c>
+      <c r="G115" t="s">
+        <v>158</v>
+      </c>
+      <c r="H115">
+        <v>8.5</v>
+      </c>
+      <c r="I115">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J115">
+        <v>10</v>
+      </c>
+      <c r="M115" s="1">
+        <f t="shared" si="2"/>
+        <v>8.9</v>
+      </c>
+      <c r="Q115" s="1">
+        <f t="shared" si="3"/>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>24033229</v>
+      </c>
+      <c r="B116" t="s">
+        <v>145</v>
+      </c>
+      <c r="C116" t="s">
+        <v>27</v>
+      </c>
+      <c r="D116">
+        <v>2025</v>
+      </c>
+      <c r="E116" t="s">
+        <v>156</v>
+      </c>
+      <c r="F116" t="s">
+        <v>157</v>
+      </c>
+      <c r="G116" t="s">
+        <v>158</v>
+      </c>
+      <c r="H116">
+        <v>6.5333333333333332</v>
+      </c>
+      <c r="I116">
+        <v>9.3261538461538471</v>
+      </c>
+      <c r="J116">
+        <v>6</v>
+      </c>
+      <c r="M116" s="1">
+        <f t="shared" si="2"/>
+        <v>7.2864957264957271</v>
+      </c>
+      <c r="Q116" s="1">
+        <f t="shared" si="3"/>
+        <v>7.2864957264957271</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>24033143</v>
+      </c>
+      <c r="B117" t="s">
+        <v>146</v>
+      </c>
+      <c r="C117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D117">
+        <v>2025</v>
+      </c>
+      <c r="E117" t="s">
+        <v>156</v>
+      </c>
+      <c r="F117" t="s">
+        <v>157</v>
+      </c>
+      <c r="G117" t="s">
+        <v>158</v>
+      </c>
+      <c r="H117">
+        <v>7.8</v>
+      </c>
+      <c r="I117">
+        <v>9.879999999999999</v>
+      </c>
+      <c r="J117">
+        <v>10</v>
+      </c>
+      <c r="M117" s="1">
+        <f t="shared" si="2"/>
+        <v>9.2266666666666666</v>
+      </c>
+      <c r="Q117" s="1">
+        <f t="shared" si="3"/>
+        <v>9.2266666666666666</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>24033421</v>
+      </c>
+      <c r="B118" t="s">
+        <v>147</v>
+      </c>
+      <c r="C118" t="s">
+        <v>27</v>
+      </c>
+      <c r="D118">
+        <v>2025</v>
+      </c>
+      <c r="E118" t="s">
+        <v>156</v>
+      </c>
+      <c r="F118" t="s">
+        <v>157</v>
+      </c>
+      <c r="G118" t="s">
+        <v>158</v>
+      </c>
+      <c r="H118">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I118">
+        <v>9.879999999999999</v>
+      </c>
+      <c r="J118">
+        <v>10</v>
+      </c>
+      <c r="M118" s="1">
+        <f t="shared" si="2"/>
+        <v>9.5266666666666655</v>
+      </c>
+      <c r="Q118" s="1">
+        <f t="shared" si="3"/>
+        <v>9.5266666666666655</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>24033308</v>
+      </c>
+      <c r="B119" t="s">
+        <v>148</v>
+      </c>
+      <c r="C119" t="s">
+        <v>27</v>
+      </c>
+      <c r="D119">
+        <v>2025</v>
+      </c>
+      <c r="E119" t="s">
+        <v>156</v>
+      </c>
+      <c r="F119" t="s">
+        <v>157</v>
+      </c>
+      <c r="G119" t="s">
+        <v>158</v>
+      </c>
+      <c r="H119">
+        <v>6.5</v>
+      </c>
+      <c r="I119">
+        <v>8.838461538461539</v>
+      </c>
+      <c r="J119">
+        <v>10</v>
+      </c>
+      <c r="M119" s="1">
+        <f t="shared" si="2"/>
+        <v>8.4461538461538463</v>
+      </c>
+      <c r="Q119" s="1">
+        <f t="shared" si="3"/>
+        <v>8.4461538461538463</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>24033356</v>
+      </c>
+      <c r="B120" t="s">
+        <v>149</v>
+      </c>
+      <c r="C120" t="s">
+        <v>27</v>
+      </c>
+      <c r="D120">
+        <v>2025</v>
+      </c>
+      <c r="E120" t="s">
+        <v>156</v>
+      </c>
+      <c r="F120" t="s">
+        <v>157</v>
+      </c>
+      <c r="G120" t="s">
+        <v>158</v>
+      </c>
+      <c r="H120">
+        <v>9.0333333333333332</v>
+      </c>
+      <c r="I120">
+        <v>9.7692307692307701</v>
+      </c>
+      <c r="J120">
+        <v>10</v>
+      </c>
+      <c r="M120" s="1">
+        <f t="shared" si="2"/>
+        <v>9.6008547008547023</v>
+      </c>
+      <c r="Q120" s="1">
+        <f t="shared" si="3"/>
+        <v>9.6008547008547023</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>24033191</v>
+      </c>
+      <c r="B121" t="s">
+        <v>150</v>
+      </c>
+      <c r="C121" t="s">
+        <v>28</v>
+      </c>
+      <c r="D121">
+        <v>2025</v>
+      </c>
+      <c r="E121" t="s">
+        <v>156</v>
+      </c>
+      <c r="F121" t="s">
+        <v>157</v>
+      </c>
+      <c r="G121" t="s">
+        <v>158</v>
+      </c>
+      <c r="H121">
+        <v>6.5</v>
+      </c>
+      <c r="I121">
+        <v>9.3923076923076927</v>
+      </c>
+      <c r="J121">
+        <v>10</v>
+      </c>
+      <c r="M121" s="1">
+        <f t="shared" si="2"/>
+        <v>8.6307692307692303</v>
+      </c>
+      <c r="Q121" s="1">
+        <f t="shared" si="3"/>
+        <v>8.6307692307692303</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>24033226</v>
+      </c>
+      <c r="B122" t="s">
+        <v>151</v>
+      </c>
+      <c r="C122" t="s">
+        <v>28</v>
+      </c>
+      <c r="D122">
+        <v>2025</v>
+      </c>
+      <c r="E122" t="s">
+        <v>156</v>
+      </c>
+      <c r="F122" t="s">
+        <v>157</v>
+      </c>
+      <c r="G122" t="s">
+        <v>158</v>
+      </c>
+      <c r="H122">
+        <v>9.6</v>
+      </c>
+      <c r="I122">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="J122">
+        <v>10</v>
+      </c>
+      <c r="M122" s="1">
+        <f t="shared" si="2"/>
+        <v>9.7666666666666657</v>
+      </c>
+      <c r="Q122" s="1">
+        <f t="shared" si="3"/>
+        <v>9.7666666666666657</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>24033376</v>
+      </c>
+      <c r="B123" t="s">
+        <v>152</v>
+      </c>
+      <c r="C123" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123">
+        <v>2025</v>
+      </c>
+      <c r="E123" t="s">
+        <v>156</v>
+      </c>
+      <c r="F123" t="s">
+        <v>157</v>
+      </c>
+      <c r="G123" t="s">
+        <v>158</v>
+      </c>
+      <c r="H123">
+        <v>10</v>
+      </c>
+      <c r="I123">
+        <v>8.7107692307692304</v>
+      </c>
+      <c r="J123">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M123" s="1">
+        <f t="shared" si="2"/>
+        <v>9.3480341880341893</v>
+      </c>
+      <c r="Q123" s="1">
+        <f t="shared" si="3"/>
+        <v>9.3480341880341893</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>24032949</v>
+      </c>
+      <c r="B124" t="s">
+        <v>153</v>
+      </c>
+      <c r="C124" t="s">
+        <v>27</v>
+      </c>
+      <c r="D124">
+        <v>2025</v>
+      </c>
+      <c r="E124" t="s">
+        <v>156</v>
+      </c>
+      <c r="F124" t="s">
+        <v>157</v>
+      </c>
+      <c r="G124" t="s">
+        <v>158</v>
+      </c>
+      <c r="H124">
+        <v>10</v>
+      </c>
+      <c r="I124">
+        <v>10</v>
+      </c>
+      <c r="J124">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M124" s="1">
+        <f t="shared" si="2"/>
+        <v>9.7777777777777786</v>
+      </c>
+      <c r="Q124" s="1">
+        <f t="shared" si="3"/>
+        <v>9.7777777777777786</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>24032898</v>
+      </c>
+      <c r="B125" t="s">
+        <v>154</v>
+      </c>
+      <c r="C125" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125">
+        <v>2025</v>
+      </c>
+      <c r="E125" t="s">
+        <v>156</v>
+      </c>
+      <c r="F125" t="s">
+        <v>157</v>
+      </c>
+      <c r="G125" t="s">
+        <v>158</v>
+      </c>
+      <c r="H125">
+        <v>7.0333333333333332</v>
+      </c>
+      <c r="I125">
+        <v>1.4923076923076923</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="M125" s="1">
+        <f t="shared" si="2"/>
+        <v>2.841880341880342</v>
+      </c>
+      <c r="Q125" s="1">
+        <f t="shared" si="3"/>
+        <v>2.841880341880342</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>24033096</v>
+      </c>
+      <c r="B126" t="s">
+        <v>155</v>
+      </c>
+      <c r="C126" t="s">
+        <v>28</v>
+      </c>
+      <c r="D126">
+        <v>2025</v>
+      </c>
+      <c r="E126" t="s">
+        <v>156</v>
+      </c>
+      <c r="F126" t="s">
+        <v>157</v>
+      </c>
+      <c r="G126" t="s">
+        <v>158</v>
+      </c>
+      <c r="H126">
+        <v>8.7333333333333343</v>
+      </c>
+      <c r="I126">
+        <v>10</v>
+      </c>
+      <c r="J126">
+        <v>10</v>
+      </c>
+      <c r="M126" s="1">
+        <f t="shared" si="2"/>
+        <v>9.5777777777777775</v>
+      </c>
+      <c r="Q126" s="1">
+        <f t="shared" si="3"/>
+        <v>9.5777777777777775</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>25013770</v>
+      </c>
+      <c r="B127" t="s">
+        <v>159</v>
+      </c>
+      <c r="C127" t="s">
+        <v>27</v>
+      </c>
+      <c r="D127">
+        <v>2025</v>
+      </c>
+      <c r="E127" t="s">
+        <v>156</v>
+      </c>
+      <c r="F127" t="s">
+        <v>165</v>
+      </c>
+      <c r="G127" t="s">
+        <v>166</v>
+      </c>
+      <c r="H127">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I127" s="4">
+        <v>8.9999999999999982</v>
+      </c>
+      <c r="J127">
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="M127" s="1">
+        <f t="shared" si="2"/>
+        <v>8.8222222222222211</v>
+      </c>
+      <c r="Q127" s="1">
+        <f t="shared" si="3"/>
+        <v>8.8222222222222211</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>25013788</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128">
+        <v>2025</v>
+      </c>
+      <c r="E128" t="s">
+        <v>156</v>
+      </c>
+      <c r="F128" t="s">
+        <v>165</v>
+      </c>
+      <c r="G128" t="s">
+        <v>166</v>
+      </c>
+      <c r="H128">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I128" s="4">
+        <v>10.1</v>
+      </c>
+      <c r="J128">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M128" s="1">
+        <f t="shared" si="2"/>
+        <v>9.2111111111111104</v>
+      </c>
+      <c r="Q128" s="1">
+        <f t="shared" si="3"/>
+        <v>9.2111111111111104</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>25013760</v>
+      </c>
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" t="s">
+        <v>27</v>
+      </c>
+      <c r="D129">
+        <v>2025</v>
+      </c>
+      <c r="E129" t="s">
+        <v>156</v>
+      </c>
+      <c r="F129" t="s">
+        <v>165</v>
+      </c>
+      <c r="G129" t="s">
+        <v>166</v>
+      </c>
+      <c r="H129">
+        <v>8.5</v>
+      </c>
+      <c r="I129" s="4">
+        <v>7.9999999999999991</v>
+      </c>
+      <c r="J129">
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="M129" s="1">
+        <f t="shared" si="2"/>
+        <v>8.3888888888888893</v>
+      </c>
+      <c r="Q129" s="1">
+        <f t="shared" si="3"/>
+        <v>8.3888888888888893</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>25013767</v>
+      </c>
+      <c r="B130" t="s">
+        <v>18</v>
+      </c>
+      <c r="C130" t="s">
+        <v>28</v>
+      </c>
+      <c r="D130">
+        <v>2025</v>
+      </c>
+      <c r="E130" t="s">
+        <v>156</v>
+      </c>
+      <c r="F130" t="s">
+        <v>165</v>
+      </c>
+      <c r="G130" t="s">
+        <v>166</v>
+      </c>
+      <c r="H130">
+        <v>4.9666666666666668</v>
+      </c>
+      <c r="I130" s="4">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="M130" s="1">
+        <f t="shared" si="2"/>
+        <v>1.6555555555555557</v>
+      </c>
+      <c r="Q130" s="1">
+        <f t="shared" si="3"/>
+        <v>1.6555555555555557</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>25013740</v>
+      </c>
+      <c r="B131" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131">
+        <v>2025</v>
+      </c>
+      <c r="E131" t="s">
+        <v>156</v>
+      </c>
+      <c r="F131" t="s">
+        <v>165</v>
+      </c>
+      <c r="G131" t="s">
+        <v>166</v>
+      </c>
+      <c r="H131">
+        <v>7.5333333333333341</v>
+      </c>
+      <c r="I131" s="4">
+        <v>7.9999999999999991</v>
+      </c>
+      <c r="J131">
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="M131" s="1">
+        <f t="shared" ref="M131:M194" si="4">AVERAGE(H131:L131)</f>
+        <v>8.0666666666666682</v>
+      </c>
+      <c r="Q131" s="1">
+        <f t="shared" ref="Q131:Q194" si="5">MAX(M131,O131,P131)</f>
+        <v>8.0666666666666682</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>25013035</v>
+      </c>
+      <c r="B132" t="s">
+        <v>160</v>
+      </c>
+      <c r="C132" t="s">
+        <v>27</v>
+      </c>
+      <c r="D132">
+        <v>2025</v>
+      </c>
+      <c r="E132" t="s">
+        <v>156</v>
+      </c>
+      <c r="F132" t="s">
+        <v>165</v>
+      </c>
+      <c r="G132" t="s">
+        <v>166</v>
+      </c>
+      <c r="H132">
+        <v>10</v>
+      </c>
+      <c r="I132" s="4">
+        <v>9</v>
+      </c>
+      <c r="J132">
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="M132" s="1">
+        <f t="shared" si="4"/>
+        <v>9.2222222222222232</v>
+      </c>
+      <c r="Q132" s="1">
+        <f t="shared" si="5"/>
+        <v>9.2222222222222232</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>25013695</v>
+      </c>
+      <c r="B133" t="s">
+        <v>161</v>
+      </c>
+      <c r="C133" t="s">
+        <v>27</v>
+      </c>
+      <c r="D133">
+        <v>2025</v>
+      </c>
+      <c r="E133" t="s">
+        <v>156</v>
+      </c>
+      <c r="F133" t="s">
+        <v>165</v>
+      </c>
+      <c r="G133" t="s">
+        <v>166</v>
+      </c>
+      <c r="H133">
+        <v>10</v>
+      </c>
+      <c r="I133" s="4">
+        <v>9</v>
+      </c>
+      <c r="J133">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M133" s="1">
+        <f t="shared" si="4"/>
+        <v>9.4444444444444446</v>
+      </c>
+      <c r="Q133" s="1">
+        <f t="shared" si="5"/>
+        <v>9.4444444444444446</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>25013736</v>
+      </c>
+      <c r="B134" t="s">
+        <v>22</v>
+      </c>
+      <c r="C134" t="s">
+        <v>27</v>
+      </c>
+      <c r="D134">
+        <v>2025</v>
+      </c>
+      <c r="E134" t="s">
+        <v>156</v>
+      </c>
+      <c r="F134" t="s">
+        <v>165</v>
+      </c>
+      <c r="G134" t="s">
+        <v>166</v>
+      </c>
+      <c r="H134">
+        <v>7.9999999999999991</v>
+      </c>
+      <c r="I134" s="4">
+        <v>9</v>
+      </c>
+      <c r="J134">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="M134" s="1">
+        <f t="shared" si="4"/>
+        <v>8.7777777777777786</v>
+      </c>
+      <c r="Q134" s="1">
+        <f t="shared" si="5"/>
+        <v>8.7777777777777786</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>25013735</v>
+      </c>
+      <c r="B135" t="s">
+        <v>162</v>
+      </c>
+      <c r="C135" t="s">
+        <v>27</v>
+      </c>
+      <c r="D135">
+        <v>2025</v>
+      </c>
+      <c r="E135" t="s">
+        <v>156</v>
+      </c>
+      <c r="F135" t="s">
+        <v>165</v>
+      </c>
+      <c r="G135" t="s">
+        <v>166</v>
+      </c>
+      <c r="H135">
+        <v>8.0333333333333332</v>
+      </c>
+      <c r="I135" s="4">
+        <v>8</v>
+      </c>
+      <c r="J135">
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="M135" s="1">
+        <f t="shared" si="4"/>
+        <v>8.2333333333333325</v>
+      </c>
+      <c r="Q135" s="1">
+        <f t="shared" si="5"/>
+        <v>8.2333333333333325</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>25013779</v>
+      </c>
+      <c r="B136" t="s">
+        <v>163</v>
+      </c>
+      <c r="C136" t="s">
+        <v>27</v>
+      </c>
+      <c r="D136">
+        <v>2025</v>
+      </c>
+      <c r="E136" t="s">
+        <v>156</v>
+      </c>
+      <c r="F136" t="s">
+        <v>165</v>
+      </c>
+      <c r="G136" t="s">
+        <v>166</v>
+      </c>
+      <c r="H136">
+        <v>8.033333333333335</v>
+      </c>
+      <c r="I136" s="4">
+        <v>5</v>
+      </c>
+      <c r="J136">
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="M136" s="1">
+        <f t="shared" si="4"/>
+        <v>4.5666666666666673</v>
+      </c>
+      <c r="Q136" s="1">
+        <f t="shared" si="5"/>
+        <v>4.5666666666666673</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>25011687</v>
+      </c>
+      <c r="B137" t="s">
+        <v>164</v>
+      </c>
+      <c r="C137" t="s">
+        <v>28</v>
+      </c>
+      <c r="D137">
+        <v>2025</v>
+      </c>
+      <c r="E137" t="s">
+        <v>156</v>
+      </c>
+      <c r="F137" t="s">
+        <v>165</v>
+      </c>
+      <c r="G137" t="s">
+        <v>166</v>
+      </c>
+      <c r="H137">
+        <v>10</v>
+      </c>
+      <c r="I137" s="4">
+        <v>9</v>
+      </c>
+      <c r="J137">
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="M137" s="1">
+        <f t="shared" si="4"/>
+        <v>9.2222222222222232</v>
+      </c>
+      <c r="Q137" s="1">
+        <f t="shared" si="5"/>
+        <v>9.2222222222222232</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>24033441</v>
+      </c>
+      <c r="B138" t="s">
+        <v>131</v>
+      </c>
+      <c r="C138" t="s">
+        <v>27</v>
+      </c>
+      <c r="D138">
+        <v>2025</v>
+      </c>
+      <c r="E138" t="s">
+        <v>156</v>
+      </c>
+      <c r="F138" t="s">
+        <v>173</v>
+      </c>
+      <c r="G138" t="s">
+        <v>158</v>
+      </c>
+      <c r="H138">
+        <v>8.4666666666666668</v>
+      </c>
+      <c r="I138">
+        <v>7.0142857142857142</v>
+      </c>
+      <c r="J138">
+        <v>7.6</v>
+      </c>
+      <c r="K138">
+        <v>10</v>
+      </c>
+      <c r="M138" s="1">
+        <f t="shared" si="4"/>
+        <v>8.2702380952380956</v>
+      </c>
+      <c r="Q138" s="1">
+        <f t="shared" si="5"/>
+        <v>8.2702380952380956</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>24033586</v>
+      </c>
+      <c r="B139" t="s">
+        <v>167</v>
+      </c>
+      <c r="C139" t="s">
+        <v>28</v>
+      </c>
+      <c r="D139">
+        <v>2025</v>
+      </c>
+      <c r="E139" t="s">
+        <v>156</v>
+      </c>
+      <c r="F139" t="s">
+        <v>173</v>
+      </c>
+      <c r="G139" t="s">
+        <v>158</v>
+      </c>
+      <c r="H139">
+        <v>9.5333333333333332</v>
+      </c>
+      <c r="I139">
+        <v>10.028571428571428</v>
+      </c>
+      <c r="J139">
+        <v>10</v>
+      </c>
+      <c r="K139">
+        <v>10</v>
+      </c>
+      <c r="M139" s="1">
+        <f t="shared" si="4"/>
+        <v>9.8904761904761909</v>
+      </c>
+      <c r="Q139" s="1">
+        <f t="shared" si="5"/>
+        <v>9.8904761904761909</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>24033161</v>
+      </c>
+      <c r="B140" t="s">
+        <v>168</v>
+      </c>
+      <c r="C140" t="s">
+        <v>28</v>
+      </c>
+      <c r="D140">
+        <v>2025</v>
+      </c>
+      <c r="E140" t="s">
+        <v>156</v>
+      </c>
+      <c r="F140" t="s">
+        <v>173</v>
+      </c>
+      <c r="G140" t="s">
+        <v>158</v>
+      </c>
+      <c r="H140">
+        <v>6.4666666666666668</v>
+      </c>
+      <c r="I140">
+        <v>7.6285714285714281</v>
+      </c>
+      <c r="J140">
+        <v>7.6</v>
+      </c>
+      <c r="K140">
+        <v>10</v>
+      </c>
+      <c r="M140" s="1">
+        <f t="shared" si="4"/>
+        <v>7.9238095238095241</v>
+      </c>
+      <c r="Q140" s="1">
+        <f t="shared" si="5"/>
+        <v>7.9238095238095241</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>24033450</v>
+      </c>
+      <c r="B141" t="s">
+        <v>134</v>
+      </c>
+      <c r="C141" t="s">
+        <v>28</v>
+      </c>
+      <c r="D141">
+        <v>2025</v>
+      </c>
+      <c r="E141" t="s">
+        <v>156</v>
+      </c>
+      <c r="F141" t="s">
+        <v>173</v>
+      </c>
+      <c r="G141" t="s">
+        <v>158</v>
+      </c>
+      <c r="H141">
+        <v>9.1</v>
+      </c>
+      <c r="I141">
+        <v>8.5</v>
+      </c>
+      <c r="J141">
+        <v>8</v>
+      </c>
+      <c r="K141">
+        <v>10</v>
+      </c>
+      <c r="M141" s="1">
+        <f t="shared" si="4"/>
+        <v>8.9</v>
+      </c>
+      <c r="Q141" s="1">
+        <f t="shared" si="5"/>
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>24033384</v>
+      </c>
+      <c r="B142" t="s">
+        <v>169</v>
+      </c>
+      <c r="C142" t="s">
+        <v>27</v>
+      </c>
+      <c r="D142">
+        <v>2025</v>
+      </c>
+      <c r="E142" t="s">
+        <v>156</v>
+      </c>
+      <c r="F142" t="s">
+        <v>173</v>
+      </c>
+      <c r="G142" t="s">
+        <v>158</v>
+      </c>
+      <c r="H142">
+        <v>4.9666666666666668</v>
+      </c>
+      <c r="I142">
+        <v>2.3714285714285714</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="M142" s="1">
+        <f t="shared" si="4"/>
+        <v>1.8345238095238097</v>
+      </c>
+      <c r="Q142" s="1">
+        <f t="shared" si="5"/>
+        <v>1.8345238095238097</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>24033611</v>
+      </c>
+      <c r="B143" t="s">
+        <v>170</v>
+      </c>
+      <c r="C143" t="s">
+        <v>27</v>
+      </c>
+      <c r="D143">
+        <v>2025</v>
+      </c>
+      <c r="E143" t="s">
+        <v>156</v>
+      </c>
+      <c r="F143" t="s">
+        <v>173</v>
+      </c>
+      <c r="G143" t="s">
+        <v>158</v>
+      </c>
+      <c r="H143">
+        <v>7.9666666666666668</v>
+      </c>
+      <c r="I143">
+        <v>8</v>
+      </c>
+      <c r="J143">
+        <v>7.6</v>
+      </c>
+      <c r="K143">
+        <v>10</v>
+      </c>
+      <c r="M143" s="1">
+        <f t="shared" si="4"/>
+        <v>8.3916666666666657</v>
+      </c>
+      <c r="Q143" s="1">
+        <f t="shared" si="5"/>
+        <v>8.3916666666666657</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>24033129</v>
+      </c>
+      <c r="B144" t="s">
+        <v>137</v>
+      </c>
+      <c r="C144" t="s">
+        <v>28</v>
+      </c>
+      <c r="D144">
+        <v>2025</v>
+      </c>
+      <c r="E144" t="s">
+        <v>156</v>
+      </c>
+      <c r="F144" t="s">
+        <v>173</v>
+      </c>
+      <c r="G144" t="s">
+        <v>158</v>
+      </c>
+      <c r="H144">
+        <v>10</v>
+      </c>
+      <c r="I144">
+        <v>10</v>
+      </c>
+      <c r="J144">
+        <v>10</v>
+      </c>
+      <c r="K144">
+        <v>10</v>
+      </c>
+      <c r="M144" s="1">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="Q144" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>24033036</v>
+      </c>
+      <c r="B145" t="s">
+        <v>138</v>
+      </c>
+      <c r="C145" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145">
+        <v>2025</v>
+      </c>
+      <c r="E145" t="s">
+        <v>156</v>
+      </c>
+      <c r="F145" t="s">
+        <v>173</v>
+      </c>
+      <c r="G145" t="s">
+        <v>158</v>
+      </c>
+      <c r="H145">
+        <v>10</v>
+      </c>
+      <c r="I145">
+        <v>10.014285714285716</v>
+      </c>
+      <c r="J145">
+        <v>10</v>
+      </c>
+      <c r="K145">
+        <v>10</v>
+      </c>
+      <c r="M145" s="1">
+        <f t="shared" si="4"/>
+        <v>10.00357142857143</v>
+      </c>
+      <c r="Q145" s="1">
+        <f t="shared" si="5"/>
+        <v>10.00357142857143</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>24033306</v>
+      </c>
+      <c r="B146" t="s">
+        <v>139</v>
+      </c>
+      <c r="C146" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146">
+        <v>2025</v>
+      </c>
+      <c r="E146" t="s">
+        <v>156</v>
+      </c>
+      <c r="F146" t="s">
+        <v>173</v>
+      </c>
+      <c r="G146" t="s">
+        <v>158</v>
+      </c>
+      <c r="H146">
+        <v>9.1</v>
+      </c>
+      <c r="I146">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="J146">
+        <v>5.6</v>
+      </c>
+      <c r="K146">
+        <v>10</v>
+      </c>
+      <c r="M146" s="1">
+        <f t="shared" si="4"/>
+        <v>7.9250000000000007</v>
+      </c>
+      <c r="Q146" s="1">
+        <f t="shared" si="5"/>
+        <v>7.9250000000000007</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>24033244</v>
+      </c>
+      <c r="B147" t="s">
+        <v>140</v>
+      </c>
+      <c r="C147" t="s">
+        <v>27</v>
+      </c>
+      <c r="D147">
+        <v>2025</v>
+      </c>
+      <c r="E147" t="s">
+        <v>156</v>
+      </c>
+      <c r="F147" t="s">
+        <v>173</v>
+      </c>
+      <c r="G147" t="s">
+        <v>158</v>
+      </c>
+      <c r="H147">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I147">
+        <v>10</v>
+      </c>
+      <c r="J147">
+        <v>10</v>
+      </c>
+      <c r="K147">
+        <v>10</v>
+      </c>
+      <c r="M147" s="1">
+        <f t="shared" si="4"/>
+        <v>9.9250000000000007</v>
+      </c>
+      <c r="Q147" s="1">
+        <f t="shared" si="5"/>
+        <v>9.9250000000000007</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>24033460</v>
+      </c>
+      <c r="B148" t="s">
+        <v>141</v>
+      </c>
+      <c r="C148" t="s">
+        <v>27</v>
+      </c>
+      <c r="D148">
+        <v>2025</v>
+      </c>
+      <c r="E148" t="s">
+        <v>156</v>
+      </c>
+      <c r="F148" t="s">
+        <v>173</v>
+      </c>
+      <c r="G148" t="s">
+        <v>158</v>
+      </c>
+      <c r="H148">
+        <v>9.4999999999999982</v>
+      </c>
+      <c r="I148">
+        <v>8.6</v>
+      </c>
+      <c r="J148">
+        <v>7.6</v>
+      </c>
+      <c r="K148">
+        <v>10</v>
+      </c>
+      <c r="M148" s="1">
+        <f t="shared" si="4"/>
+        <v>8.9249999999999989</v>
+      </c>
+      <c r="Q148" s="1">
+        <f t="shared" si="5"/>
+        <v>8.9249999999999989</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>24033435</v>
+      </c>
+      <c r="B149" t="s">
+        <v>171</v>
+      </c>
+      <c r="C149" t="s">
+        <v>27</v>
+      </c>
+      <c r="D149">
+        <v>2025</v>
+      </c>
+      <c r="E149" t="s">
+        <v>156</v>
+      </c>
+      <c r="F149" t="s">
+        <v>173</v>
+      </c>
+      <c r="G149" t="s">
+        <v>158</v>
+      </c>
+      <c r="H149">
+        <v>9.9666666666666668</v>
+      </c>
+      <c r="I149">
+        <v>8.5</v>
+      </c>
+      <c r="J149">
+        <v>10</v>
+      </c>
+      <c r="K149">
+        <v>10</v>
+      </c>
+      <c r="M149" s="1">
+        <f t="shared" si="4"/>
+        <v>9.6166666666666671</v>
+      </c>
+      <c r="Q149" s="1">
+        <f t="shared" si="5"/>
+        <v>9.6166666666666671</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>24033330</v>
+      </c>
+      <c r="B150" t="s">
+        <v>143</v>
+      </c>
+      <c r="C150" t="s">
+        <v>28</v>
+      </c>
+      <c r="D150">
+        <v>2025</v>
+      </c>
+      <c r="E150" t="s">
+        <v>156</v>
+      </c>
+      <c r="F150" t="s">
+        <v>173</v>
+      </c>
+      <c r="G150" t="s">
+        <v>158</v>
+      </c>
+      <c r="H150">
+        <v>9.4999999999999982</v>
+      </c>
+      <c r="I150">
+        <v>8.5142857142857142</v>
+      </c>
+      <c r="J150">
+        <v>7.6</v>
+      </c>
+      <c r="K150">
+        <v>10</v>
+      </c>
+      <c r="M150" s="1">
+        <f t="shared" si="4"/>
+        <v>8.9035714285714285</v>
+      </c>
+      <c r="Q150" s="1">
+        <f t="shared" si="5"/>
+        <v>8.9035714285714285</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>24032968</v>
+      </c>
+      <c r="B151" t="s">
+        <v>144</v>
+      </c>
+      <c r="C151" t="s">
+        <v>28</v>
+      </c>
+      <c r="D151">
+        <v>2025</v>
+      </c>
+      <c r="E151" t="s">
+        <v>156</v>
+      </c>
+      <c r="F151" t="s">
+        <v>173</v>
+      </c>
+      <c r="G151" t="s">
+        <v>158</v>
+      </c>
+      <c r="H151">
+        <v>9</v>
+      </c>
+      <c r="I151">
+        <v>9.5</v>
+      </c>
+      <c r="J151">
+        <v>10</v>
+      </c>
+      <c r="K151">
+        <v>10</v>
+      </c>
+      <c r="M151" s="1">
+        <f t="shared" si="4"/>
+        <v>9.625</v>
+      </c>
+      <c r="Q151" s="1">
+        <f t="shared" si="5"/>
+        <v>9.625</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>24033229</v>
+      </c>
+      <c r="B152" t="s">
+        <v>145</v>
+      </c>
+      <c r="C152" t="s">
+        <v>27</v>
+      </c>
+      <c r="D152">
+        <v>2025</v>
+      </c>
+      <c r="E152" t="s">
+        <v>156</v>
+      </c>
+      <c r="F152" t="s">
+        <v>173</v>
+      </c>
+      <c r="G152" t="s">
+        <v>158</v>
+      </c>
+      <c r="H152">
+        <v>8.0333333333333332</v>
+      </c>
+      <c r="I152">
+        <v>4.9857142857142858</v>
+      </c>
+      <c r="J152">
+        <v>5.6</v>
+      </c>
+      <c r="K152">
+        <v>10</v>
+      </c>
+      <c r="M152" s="1">
+        <f t="shared" si="4"/>
+        <v>7.1547619047619051</v>
+      </c>
+      <c r="Q152" s="1">
+        <f t="shared" si="5"/>
+        <v>7.1547619047619051</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>24033143</v>
+      </c>
+      <c r="B153" t="s">
+        <v>146</v>
+      </c>
+      <c r="C153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D153">
+        <v>2025</v>
+      </c>
+      <c r="E153" t="s">
+        <v>156</v>
+      </c>
+      <c r="F153" t="s">
+        <v>173</v>
+      </c>
+      <c r="G153" t="s">
+        <v>158</v>
+      </c>
+      <c r="H153">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I153">
+        <v>8</v>
+      </c>
+      <c r="J153">
+        <v>10</v>
+      </c>
+      <c r="K153">
+        <v>10</v>
+      </c>
+      <c r="M153" s="1">
+        <f t="shared" si="4"/>
+        <v>9.4250000000000007</v>
+      </c>
+      <c r="Q153" s="1">
+        <f t="shared" si="5"/>
+        <v>9.4250000000000007</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>24033421</v>
+      </c>
+      <c r="B154" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" t="s">
+        <v>27</v>
+      </c>
+      <c r="D154">
+        <v>2025</v>
+      </c>
+      <c r="E154" t="s">
+        <v>156</v>
+      </c>
+      <c r="F154" t="s">
+        <v>173</v>
+      </c>
+      <c r="G154" t="s">
+        <v>158</v>
+      </c>
+      <c r="H154">
+        <v>9.1</v>
+      </c>
+      <c r="I154">
+        <v>10</v>
+      </c>
+      <c r="J154">
+        <v>10</v>
+      </c>
+      <c r="K154">
+        <v>10</v>
+      </c>
+      <c r="M154" s="1">
+        <f t="shared" si="4"/>
+        <v>9.7750000000000004</v>
+      </c>
+      <c r="Q154" s="1">
+        <f t="shared" si="5"/>
+        <v>9.7750000000000004</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>24033308</v>
+      </c>
+      <c r="B155" t="s">
+        <v>148</v>
+      </c>
+      <c r="C155" t="s">
+        <v>27</v>
+      </c>
+      <c r="D155">
+        <v>2025</v>
+      </c>
+      <c r="E155" t="s">
+        <v>156</v>
+      </c>
+      <c r="F155" t="s">
+        <v>173</v>
+      </c>
+      <c r="G155" t="s">
+        <v>158</v>
+      </c>
+      <c r="H155">
+        <v>8.9666666666666668</v>
+      </c>
+      <c r="I155">
+        <v>8.5285714285714285</v>
+      </c>
+      <c r="J155">
+        <v>7</v>
+      </c>
+      <c r="K155">
+        <v>10</v>
+      </c>
+      <c r="M155" s="1">
+        <f t="shared" si="4"/>
+        <v>8.6238095238095234</v>
+      </c>
+      <c r="Q155" s="1">
+        <f t="shared" si="5"/>
+        <v>8.6238095238095234</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>24033356</v>
+      </c>
+      <c r="B156" t="s">
+        <v>149</v>
+      </c>
+      <c r="C156" t="s">
+        <v>27</v>
+      </c>
+      <c r="D156">
+        <v>2025</v>
+      </c>
+      <c r="E156" t="s">
+        <v>156</v>
+      </c>
+      <c r="F156" t="s">
+        <v>173</v>
+      </c>
+      <c r="G156" t="s">
+        <v>158</v>
+      </c>
+      <c r="H156">
+        <v>9.1</v>
+      </c>
+      <c r="I156">
+        <v>8.5142857142857142</v>
+      </c>
+      <c r="J156">
+        <v>10</v>
+      </c>
+      <c r="K156">
+        <v>10</v>
+      </c>
+      <c r="M156" s="1">
+        <f t="shared" si="4"/>
+        <v>9.4035714285714285</v>
+      </c>
+      <c r="Q156" s="1">
+        <f t="shared" si="5"/>
+        <v>9.4035714285714285</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>24033191</v>
+      </c>
+      <c r="B157" t="s">
+        <v>150</v>
+      </c>
+      <c r="C157" t="s">
+        <v>28</v>
+      </c>
+      <c r="D157">
+        <v>2025</v>
+      </c>
+      <c r="E157" t="s">
+        <v>156</v>
+      </c>
+      <c r="F157" t="s">
+        <v>173</v>
+      </c>
+      <c r="G157" t="s">
+        <v>158</v>
+      </c>
+      <c r="H157">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I157">
+        <v>7.5142857142857142</v>
+      </c>
+      <c r="J157">
+        <v>7.6</v>
+      </c>
+      <c r="K157">
+        <v>10</v>
+      </c>
+      <c r="M157" s="1">
+        <f t="shared" si="4"/>
+        <v>8.4785714285714295</v>
+      </c>
+      <c r="Q157" s="1">
+        <f t="shared" si="5"/>
+        <v>8.4785714285714295</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>24033226</v>
+      </c>
+      <c r="B158" t="s">
+        <v>151</v>
+      </c>
+      <c r="C158" t="s">
+        <v>28</v>
+      </c>
+      <c r="D158">
+        <v>2025</v>
+      </c>
+      <c r="E158" t="s">
+        <v>156</v>
+      </c>
+      <c r="F158" t="s">
+        <v>173</v>
+      </c>
+      <c r="G158" t="s">
+        <v>158</v>
+      </c>
+      <c r="H158">
+        <v>10</v>
+      </c>
+      <c r="I158">
+        <v>10</v>
+      </c>
+      <c r="J158">
+        <v>10</v>
+      </c>
+      <c r="K158">
+        <v>10</v>
+      </c>
+      <c r="M158" s="1">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="Q158" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>24033376</v>
+      </c>
+      <c r="B159" t="s">
+        <v>152</v>
+      </c>
+      <c r="C159" t="s">
+        <v>28</v>
+      </c>
+      <c r="D159">
+        <v>2025</v>
+      </c>
+      <c r="E159" t="s">
+        <v>156</v>
+      </c>
+      <c r="F159" t="s">
+        <v>173</v>
+      </c>
+      <c r="G159" t="s">
+        <v>158</v>
+      </c>
+      <c r="H159">
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="I159">
+        <v>10.014285714285716</v>
+      </c>
+      <c r="J159">
+        <v>10</v>
+      </c>
+      <c r="K159">
+        <v>10</v>
+      </c>
+      <c r="M159" s="1">
+        <f t="shared" si="4"/>
+        <v>9.836904761904762</v>
+      </c>
+      <c r="Q159" s="1">
+        <f t="shared" si="5"/>
+        <v>9.836904761904762</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>24032949</v>
+      </c>
+      <c r="B160" t="s">
+        <v>153</v>
+      </c>
+      <c r="C160" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160">
+        <v>2025</v>
+      </c>
+      <c r="E160" t="s">
+        <v>156</v>
+      </c>
+      <c r="F160" t="s">
+        <v>173</v>
+      </c>
+      <c r="G160" t="s">
+        <v>158</v>
+      </c>
+      <c r="H160">
+        <v>10</v>
+      </c>
+      <c r="I160">
+        <v>10.014285714285716</v>
+      </c>
+      <c r="J160">
+        <v>7</v>
+      </c>
+      <c r="K160">
+        <v>10</v>
+      </c>
+      <c r="M160" s="1">
+        <f t="shared" si="4"/>
+        <v>9.2535714285714299</v>
+      </c>
+      <c r="Q160" s="1">
+        <f t="shared" si="5"/>
+        <v>9.2535714285714299</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>24032898</v>
+      </c>
+      <c r="B161" t="s">
+        <v>172</v>
+      </c>
+      <c r="C161" t="s">
+        <v>28</v>
+      </c>
+      <c r="D161">
+        <v>2025</v>
+      </c>
+      <c r="E161" t="s">
+        <v>156</v>
+      </c>
+      <c r="F161" t="s">
+        <v>173</v>
+      </c>
+      <c r="G161" t="s">
+        <v>158</v>
+      </c>
+      <c r="H161">
+        <v>6.4666666666666668</v>
+      </c>
+      <c r="I161">
+        <v>1.6571428571428573</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="M161" s="1">
+        <f t="shared" si="4"/>
+        <v>2.0309523809523808</v>
+      </c>
+      <c r="Q161" s="1">
+        <f t="shared" si="5"/>
+        <v>2.0309523809523808</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>24033096</v>
+      </c>
+      <c r="B162" t="s">
+        <v>155</v>
+      </c>
+      <c r="C162" t="s">
+        <v>28</v>
+      </c>
+      <c r="D162">
+        <v>2025</v>
+      </c>
+      <c r="E162" t="s">
+        <v>156</v>
+      </c>
+      <c r="F162" t="s">
+        <v>173</v>
+      </c>
+      <c r="G162" t="s">
+        <v>158</v>
+      </c>
+      <c r="H162">
+        <v>9.1</v>
+      </c>
+      <c r="I162">
+        <v>8</v>
+      </c>
+      <c r="J162">
+        <v>7.6</v>
+      </c>
+      <c r="K162">
+        <v>10</v>
+      </c>
+      <c r="M162" s="1">
+        <f t="shared" si="4"/>
+        <v>8.6750000000000007</v>
+      </c>
+      <c r="Q162" s="1">
+        <f t="shared" si="5"/>
+        <v>8.6750000000000007</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A163" s="3">
+        <v>24032989</v>
+      </c>
+      <c r="B163" t="s">
+        <v>174</v>
+      </c>
+      <c r="C163" t="s">
+        <v>27</v>
+      </c>
+      <c r="D163">
+        <v>2025</v>
+      </c>
+      <c r="E163" t="s">
+        <v>156</v>
+      </c>
+      <c r="F163" t="s">
+        <v>173</v>
+      </c>
+      <c r="G163" t="s">
+        <v>197</v>
+      </c>
+      <c r="H163">
+        <v>9.6</v>
+      </c>
+      <c r="I163">
+        <v>9</v>
+      </c>
+      <c r="J163">
+        <v>5.6</v>
+      </c>
+      <c r="K163">
+        <v>10</v>
+      </c>
+      <c r="M163" s="1">
+        <f t="shared" si="4"/>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="Q163" s="1">
+        <f t="shared" si="5"/>
+        <v>8.5500000000000007</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>24033522</v>
+      </c>
+      <c r="B164" t="s">
+        <v>175</v>
+      </c>
+      <c r="C164" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164">
+        <v>2025</v>
+      </c>
+      <c r="E164" t="s">
+        <v>156</v>
+      </c>
+      <c r="F164" t="s">
+        <v>173</v>
+      </c>
+      <c r="G164" t="s">
+        <v>197</v>
+      </c>
+      <c r="H164">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I164">
+        <v>10</v>
+      </c>
+      <c r="J164">
+        <v>10</v>
+      </c>
+      <c r="K164">
+        <v>10</v>
+      </c>
+      <c r="M164" s="1">
+        <f t="shared" si="4"/>
+        <v>9.9250000000000007</v>
+      </c>
+      <c r="Q164" s="1">
+        <f t="shared" si="5"/>
+        <v>9.9250000000000007</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>24032904</v>
+      </c>
+      <c r="B165" t="s">
+        <v>176</v>
+      </c>
+      <c r="C165" t="s">
+        <v>27</v>
+      </c>
+      <c r="D165">
+        <v>2025</v>
+      </c>
+      <c r="E165" t="s">
+        <v>156</v>
+      </c>
+      <c r="F165" t="s">
+        <v>173</v>
+      </c>
+      <c r="G165" t="s">
+        <v>197</v>
+      </c>
+      <c r="H165">
+        <v>8.0333333333333332</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="M165" s="1">
+        <f t="shared" si="4"/>
+        <v>2.5083333333333333</v>
+      </c>
+      <c r="Q165" s="1">
+        <f t="shared" si="5"/>
+        <v>2.5083333333333333</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>24032939</v>
+      </c>
+      <c r="B166" t="s">
+        <v>177</v>
+      </c>
+      <c r="C166" t="s">
+        <v>27</v>
+      </c>
+      <c r="D166">
+        <v>2025</v>
+      </c>
+      <c r="E166" t="s">
+        <v>156</v>
+      </c>
+      <c r="F166" t="s">
+        <v>173</v>
+      </c>
+      <c r="G166" t="s">
+        <v>197</v>
+      </c>
+      <c r="H166">
+        <v>10</v>
+      </c>
+      <c r="I166">
+        <v>9</v>
+      </c>
+      <c r="J166">
+        <v>10</v>
+      </c>
+      <c r="K166">
+        <v>10</v>
+      </c>
+      <c r="M166" s="1">
+        <f t="shared" si="4"/>
+        <v>9.75</v>
+      </c>
+      <c r="Q166" s="1">
+        <f t="shared" si="5"/>
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>24033176</v>
+      </c>
+      <c r="B167" t="s">
+        <v>178</v>
+      </c>
+      <c r="C167" t="s">
+        <v>28</v>
+      </c>
+      <c r="D167">
+        <v>2025</v>
+      </c>
+      <c r="E167" t="s">
+        <v>156</v>
+      </c>
+      <c r="F167" t="s">
+        <v>173</v>
+      </c>
+      <c r="G167" t="s">
+        <v>197</v>
+      </c>
+      <c r="H167">
+        <v>10</v>
+      </c>
+      <c r="I167">
+        <v>8.5</v>
+      </c>
+      <c r="J167">
+        <v>10</v>
+      </c>
+      <c r="K167">
+        <v>10</v>
+      </c>
+      <c r="M167" s="1">
+        <f t="shared" si="4"/>
+        <v>9.625</v>
+      </c>
+      <c r="Q167" s="1">
+        <f t="shared" si="5"/>
+        <v>9.625</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>24033430</v>
+      </c>
+      <c r="B168" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" t="s">
+        <v>27</v>
+      </c>
+      <c r="D168">
+        <v>2025</v>
+      </c>
+      <c r="E168" t="s">
+        <v>156</v>
+      </c>
+      <c r="F168" t="s">
+        <v>173</v>
+      </c>
+      <c r="G168" t="s">
+        <v>197</v>
+      </c>
+      <c r="H168">
+        <v>10</v>
+      </c>
+      <c r="I168">
+        <v>10</v>
+      </c>
+      <c r="J168">
+        <v>8</v>
+      </c>
+      <c r="K168">
+        <v>10</v>
+      </c>
+      <c r="M168" s="1">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="Q168" s="1">
+        <f t="shared" si="5"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>24033501</v>
+      </c>
+      <c r="B169" t="s">
+        <v>180</v>
+      </c>
+      <c r="C169" t="s">
+        <v>27</v>
+      </c>
+      <c r="D169">
+        <v>2025</v>
+      </c>
+      <c r="E169" t="s">
+        <v>156</v>
+      </c>
+      <c r="F169" t="s">
+        <v>173</v>
+      </c>
+      <c r="G169" t="s">
+        <v>197</v>
+      </c>
+      <c r="H169">
+        <v>8.5666666666666664</v>
+      </c>
+      <c r="I169">
+        <v>7</v>
+      </c>
+      <c r="J169">
+        <v>8</v>
+      </c>
+      <c r="K169">
+        <v>10</v>
+      </c>
+      <c r="M169" s="1">
+        <f t="shared" si="4"/>
+        <v>8.3916666666666657</v>
+      </c>
+      <c r="Q169" s="1">
+        <f t="shared" si="5"/>
+        <v>8.3916666666666657</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>24033127</v>
+      </c>
+      <c r="B170" t="s">
+        <v>181</v>
+      </c>
+      <c r="C170" t="s">
+        <v>28</v>
+      </c>
+      <c r="D170">
+        <v>2025</v>
+      </c>
+      <c r="E170" t="s">
+        <v>156</v>
+      </c>
+      <c r="F170" t="s">
+        <v>173</v>
+      </c>
+      <c r="G170" t="s">
+        <v>197</v>
+      </c>
+      <c r="H170">
+        <v>8.0333333333333332</v>
+      </c>
+      <c r="I170">
+        <v>5.5</v>
+      </c>
+      <c r="J170">
+        <v>7</v>
+      </c>
+      <c r="K170">
+        <v>10</v>
+      </c>
+      <c r="M170" s="1">
+        <f t="shared" si="4"/>
+        <v>7.6333333333333329</v>
+      </c>
+      <c r="Q170" s="1">
+        <f t="shared" si="5"/>
+        <v>7.6333333333333329</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>24033117</v>
+      </c>
+      <c r="B171" t="s">
+        <v>182</v>
+      </c>
+      <c r="C171" t="s">
+        <v>28</v>
+      </c>
+      <c r="D171">
+        <v>2025</v>
+      </c>
+      <c r="E171" t="s">
+        <v>156</v>
+      </c>
+      <c r="F171" t="s">
+        <v>173</v>
+      </c>
+      <c r="G171" t="s">
+        <v>197</v>
+      </c>
+      <c r="H171">
+        <v>9.9999999999999982</v>
+      </c>
+      <c r="I171">
+        <v>8.5</v>
+      </c>
+      <c r="J171">
+        <v>10</v>
+      </c>
+      <c r="K171">
+        <v>10</v>
+      </c>
+      <c r="M171" s="1">
+        <f t="shared" si="4"/>
+        <v>9.625</v>
+      </c>
+      <c r="Q171" s="1">
+        <f t="shared" si="5"/>
+        <v>9.625</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>24031533</v>
+      </c>
+      <c r="B172" t="s">
+        <v>183</v>
+      </c>
+      <c r="C172" t="s">
+        <v>27</v>
+      </c>
+      <c r="D172">
+        <v>2025</v>
+      </c>
+      <c r="E172" t="s">
+        <v>156</v>
+      </c>
+      <c r="F172" t="s">
+        <v>173</v>
+      </c>
+      <c r="G172" t="s">
+        <v>197</v>
+      </c>
+      <c r="H172">
+        <v>8.1666666666666661</v>
+      </c>
+      <c r="I172">
+        <v>7.5000000000000009</v>
+      </c>
+      <c r="J172">
+        <v>7.8</v>
+      </c>
+      <c r="K172">
+        <v>10</v>
+      </c>
+      <c r="M172" s="1">
+        <f t="shared" si="4"/>
+        <v>8.3666666666666671</v>
+      </c>
+      <c r="Q172" s="1">
+        <f t="shared" si="5"/>
+        <v>8.3666666666666671</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>24033193</v>
+      </c>
+      <c r="B173" t="s">
+        <v>184</v>
+      </c>
+      <c r="C173" t="s">
+        <v>27</v>
+      </c>
+      <c r="D173">
+        <v>2025</v>
+      </c>
+      <c r="E173" t="s">
+        <v>156</v>
+      </c>
+      <c r="F173" t="s">
+        <v>173</v>
+      </c>
+      <c r="G173" t="s">
+        <v>197</v>
+      </c>
+      <c r="H173">
+        <v>8.1333333333333346</v>
+      </c>
+      <c r="I173">
+        <v>7</v>
+      </c>
+      <c r="J173">
+        <v>8</v>
+      </c>
+      <c r="K173">
+        <v>10</v>
+      </c>
+      <c r="M173" s="1">
+        <f t="shared" si="4"/>
+        <v>8.2833333333333332</v>
+      </c>
+      <c r="Q173" s="1">
+        <f t="shared" si="5"/>
+        <v>8.2833333333333332</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>24033415</v>
+      </c>
+      <c r="B174" t="s">
+        <v>185</v>
+      </c>
+      <c r="C174" t="s">
+        <v>27</v>
+      </c>
+      <c r="D174">
+        <v>2025</v>
+      </c>
+      <c r="E174" t="s">
+        <v>156</v>
+      </c>
+      <c r="F174" t="s">
+        <v>173</v>
+      </c>
+      <c r="G174" t="s">
+        <v>197</v>
+      </c>
+      <c r="H174">
+        <v>9</v>
+      </c>
+      <c r="I174">
+        <v>8.5</v>
+      </c>
+      <c r="J174">
+        <v>9</v>
+      </c>
+      <c r="K174">
+        <v>10</v>
+      </c>
+      <c r="M174" s="1">
+        <f t="shared" si="4"/>
+        <v>9.125</v>
+      </c>
+      <c r="Q174" s="1">
+        <f t="shared" si="5"/>
+        <v>9.125</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>24033105</v>
+      </c>
+      <c r="B175" t="s">
+        <v>186</v>
+      </c>
+      <c r="C175" t="s">
+        <v>27</v>
+      </c>
+      <c r="D175">
+        <v>2025</v>
+      </c>
+      <c r="E175" t="s">
+        <v>156</v>
+      </c>
+      <c r="F175" t="s">
+        <v>173</v>
+      </c>
+      <c r="G175" t="s">
+        <v>197</v>
+      </c>
+      <c r="H175">
+        <v>9.9666666666666668</v>
+      </c>
+      <c r="I175">
+        <v>9</v>
+      </c>
+      <c r="J175">
+        <v>8</v>
+      </c>
+      <c r="K175">
+        <v>10</v>
+      </c>
+      <c r="M175" s="1">
+        <f t="shared" si="4"/>
+        <v>9.2416666666666671</v>
+      </c>
+      <c r="Q175" s="1">
+        <f t="shared" si="5"/>
+        <v>9.2416666666666671</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>24033353</v>
+      </c>
+      <c r="B176" t="s">
+        <v>187</v>
+      </c>
+      <c r="C176" t="s">
+        <v>27</v>
+      </c>
+      <c r="D176">
+        <v>2025</v>
+      </c>
+      <c r="E176" t="s">
+        <v>156</v>
+      </c>
+      <c r="F176" t="s">
+        <v>173</v>
+      </c>
+      <c r="G176" t="s">
+        <v>197</v>
+      </c>
+      <c r="H176">
+        <v>8.0333333333333332</v>
+      </c>
+      <c r="I176">
+        <v>8.5</v>
+      </c>
+      <c r="J176">
+        <v>8</v>
+      </c>
+      <c r="K176">
+        <v>10</v>
+      </c>
+      <c r="M176" s="1">
+        <f t="shared" si="4"/>
+        <v>8.6333333333333329</v>
+      </c>
+      <c r="Q176" s="1">
+        <f t="shared" si="5"/>
+        <v>8.6333333333333329</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>24033190</v>
+      </c>
+      <c r="B177" t="s">
+        <v>188</v>
+      </c>
+      <c r="C177" t="s">
+        <v>28</v>
+      </c>
+      <c r="D177">
+        <v>2025</v>
+      </c>
+      <c r="E177" t="s">
+        <v>156</v>
+      </c>
+      <c r="F177" t="s">
+        <v>173</v>
+      </c>
+      <c r="G177" t="s">
+        <v>197</v>
+      </c>
+      <c r="H177">
+        <v>10</v>
+      </c>
+      <c r="I177">
+        <v>8.5</v>
+      </c>
+      <c r="J177">
+        <v>9</v>
+      </c>
+      <c r="K177">
+        <v>10</v>
+      </c>
+      <c r="M177" s="1">
+        <f t="shared" si="4"/>
+        <v>9.375</v>
+      </c>
+      <c r="Q177" s="1">
+        <f t="shared" si="5"/>
+        <v>9.375</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>24033121</v>
+      </c>
+      <c r="B178" t="s">
+        <v>189</v>
+      </c>
+      <c r="C178" t="s">
+        <v>27</v>
+      </c>
+      <c r="D178">
+        <v>2025</v>
+      </c>
+      <c r="E178" t="s">
+        <v>156</v>
+      </c>
+      <c r="F178" t="s">
+        <v>173</v>
+      </c>
+      <c r="G178" t="s">
+        <v>197</v>
+      </c>
+      <c r="H178">
+        <v>9</v>
+      </c>
+      <c r="I178">
+        <v>8.5</v>
+      </c>
+      <c r="J178">
+        <v>5.6</v>
+      </c>
+      <c r="K178">
+        <v>10</v>
+      </c>
+      <c r="M178" s="1">
+        <f t="shared" si="4"/>
+        <v>8.2750000000000004</v>
+      </c>
+      <c r="Q178" s="1">
+        <f t="shared" si="5"/>
+        <v>8.2750000000000004</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>24033334</v>
+      </c>
+      <c r="B179" t="s">
+        <v>190</v>
+      </c>
+      <c r="C179" t="s">
+        <v>27</v>
+      </c>
+      <c r="D179">
+        <v>2025</v>
+      </c>
+      <c r="E179" t="s">
+        <v>156</v>
+      </c>
+      <c r="F179" t="s">
+        <v>173</v>
+      </c>
+      <c r="G179" t="s">
+        <v>197</v>
+      </c>
+      <c r="H179">
+        <v>8.9666666666666668</v>
+      </c>
+      <c r="I179">
+        <v>8.5</v>
+      </c>
+      <c r="J179">
+        <v>7.6</v>
+      </c>
+      <c r="K179">
+        <v>10</v>
+      </c>
+      <c r="M179" s="1">
+        <f t="shared" si="4"/>
+        <v>8.7666666666666675</v>
+      </c>
+      <c r="Q179" s="1">
+        <f t="shared" si="5"/>
+        <v>8.7666666666666675</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>24033141</v>
+      </c>
+      <c r="B180" t="s">
+        <v>191</v>
+      </c>
+      <c r="C180" t="s">
+        <v>28</v>
+      </c>
+      <c r="D180">
+        <v>2025</v>
+      </c>
+      <c r="E180" t="s">
+        <v>156</v>
+      </c>
+      <c r="F180" t="s">
+        <v>173</v>
+      </c>
+      <c r="G180" t="s">
+        <v>197</v>
+      </c>
+      <c r="H180">
+        <v>10</v>
+      </c>
+      <c r="I180">
+        <v>9</v>
+      </c>
+      <c r="J180">
+        <v>10</v>
+      </c>
+      <c r="K180">
+        <v>10</v>
+      </c>
+      <c r="M180" s="1">
+        <f t="shared" si="4"/>
+        <v>9.75</v>
+      </c>
+      <c r="Q180" s="1">
+        <f t="shared" si="5"/>
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>24033011</v>
+      </c>
+      <c r="B181" t="s">
+        <v>192</v>
+      </c>
+      <c r="C181" t="s">
+        <v>27</v>
+      </c>
+      <c r="D181">
+        <v>2025</v>
+      </c>
+      <c r="E181" t="s">
+        <v>156</v>
+      </c>
+      <c r="F181" t="s">
+        <v>173</v>
+      </c>
+      <c r="G181" t="s">
+        <v>197</v>
+      </c>
+      <c r="H181">
+        <v>10</v>
+      </c>
+      <c r="I181">
+        <v>10</v>
+      </c>
+      <c r="J181">
+        <v>10</v>
+      </c>
+      <c r="K181">
+        <v>10</v>
+      </c>
+      <c r="M181" s="1">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="Q181" s="1">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>24033524</v>
+      </c>
+      <c r="B182" t="s">
+        <v>193</v>
+      </c>
+      <c r="C182" t="s">
+        <v>28</v>
+      </c>
+      <c r="D182">
+        <v>2025</v>
+      </c>
+      <c r="E182" t="s">
+        <v>156</v>
+      </c>
+      <c r="F182" t="s">
+        <v>173</v>
+      </c>
+      <c r="G182" t="s">
+        <v>197</v>
+      </c>
+      <c r="H182">
+        <v>10</v>
+      </c>
+      <c r="I182">
+        <v>8.5</v>
+      </c>
+      <c r="J182">
+        <v>10</v>
+      </c>
+      <c r="K182">
+        <v>10</v>
+      </c>
+      <c r="M182" s="1">
+        <f t="shared" si="4"/>
+        <v>9.625</v>
+      </c>
+      <c r="Q182" s="1">
+        <f t="shared" si="5"/>
+        <v>9.625</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>24032977</v>
+      </c>
+      <c r="B183" t="s">
+        <v>194</v>
+      </c>
+      <c r="C183" t="s">
+        <v>27</v>
+      </c>
+      <c r="D183">
+        <v>2025</v>
+      </c>
+      <c r="E183" t="s">
+        <v>156</v>
+      </c>
+      <c r="F183" t="s">
+        <v>173</v>
+      </c>
+      <c r="G183" t="s">
+        <v>197</v>
+      </c>
+      <c r="H183">
+        <v>9.966666666666665</v>
+      </c>
+      <c r="I183">
+        <v>7.5000000000000009</v>
+      </c>
+      <c r="J183">
+        <v>8</v>
+      </c>
+      <c r="K183">
+        <v>10</v>
+      </c>
+      <c r="M183" s="1">
+        <f t="shared" si="4"/>
+        <v>8.8666666666666671</v>
+      </c>
+      <c r="Q183" s="1">
+        <f t="shared" si="5"/>
+        <v>8.8666666666666671</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>24033014</v>
+      </c>
+      <c r="B184" t="s">
+        <v>195</v>
+      </c>
+      <c r="C184" t="s">
+        <v>28</v>
+      </c>
+      <c r="D184">
+        <v>2025</v>
+      </c>
+      <c r="E184" t="s">
+        <v>156</v>
+      </c>
+      <c r="F184" t="s">
+        <v>173</v>
+      </c>
+      <c r="G184" t="s">
+        <v>197</v>
+      </c>
+      <c r="H184">
+        <v>9.9999999999999982</v>
+      </c>
+      <c r="I184">
+        <v>7.5000000000000009</v>
+      </c>
+      <c r="J184">
+        <v>8</v>
+      </c>
+      <c r="K184">
+        <v>10</v>
+      </c>
+      <c r="M184" s="1">
+        <f t="shared" si="4"/>
+        <v>8.875</v>
+      </c>
+      <c r="Q184" s="1">
+        <f t="shared" si="5"/>
+        <v>8.875</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>24033417</v>
+      </c>
+      <c r="B185" t="s">
+        <v>196</v>
+      </c>
+      <c r="C185" t="s">
+        <v>27</v>
+      </c>
+      <c r="D185">
+        <v>2025</v>
+      </c>
+      <c r="E185" t="s">
+        <v>156</v>
+      </c>
+      <c r="F185" t="s">
+        <v>173</v>
+      </c>
+      <c r="G185" t="s">
+        <v>197</v>
+      </c>
+      <c r="H185">
+        <v>5.9666666666666677</v>
+      </c>
+      <c r="I185">
+        <v>8.5</v>
+      </c>
+      <c r="J185">
+        <v>6.6</v>
+      </c>
+      <c r="K185">
+        <v>10</v>
+      </c>
+      <c r="M185" s="1">
+        <f t="shared" si="4"/>
+        <v>7.7666666666666675</v>
+      </c>
+      <c r="Q185" s="1">
+        <f t="shared" si="5"/>
+        <v>7.7666666666666675</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>25011687</v>
+      </c>
+      <c r="B186" t="s">
+        <v>198</v>
+      </c>
+      <c r="C186" t="s">
+        <v>28</v>
+      </c>
+      <c r="D186">
+        <v>2026</v>
+      </c>
+      <c r="E186" t="s">
+        <v>205</v>
+      </c>
+      <c r="F186" t="s">
+        <v>206</v>
+      </c>
+      <c r="G186" t="s">
+        <v>207</v>
+      </c>
+      <c r="H186">
+        <v>9</v>
+      </c>
+      <c r="I186">
+        <v>9.5</v>
+      </c>
+      <c r="M186" s="1">
+        <f t="shared" si="4"/>
+        <v>9.25</v>
+      </c>
+      <c r="Q186" s="1">
+        <f t="shared" si="5"/>
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>25013735</v>
+      </c>
+      <c r="B187" t="s">
+        <v>199</v>
+      </c>
+      <c r="C187" t="s">
+        <v>27</v>
+      </c>
+      <c r="D187">
+        <v>2026</v>
+      </c>
+      <c r="E187" t="s">
+        <v>205</v>
+      </c>
+      <c r="F187" t="s">
+        <v>206</v>
+      </c>
+      <c r="G187" t="s">
+        <v>207</v>
+      </c>
+      <c r="H187">
+        <v>6.9999999999999991</v>
+      </c>
+      <c r="I187">
+        <v>5.5</v>
+      </c>
+      <c r="M187" s="1">
+        <f t="shared" si="4"/>
+        <v>6.25</v>
+      </c>
+      <c r="Q187" s="1">
+        <f t="shared" si="5"/>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>25013035</v>
+      </c>
+      <c r="B188" t="s">
+        <v>200</v>
+      </c>
+      <c r="C188" t="s">
+        <v>27</v>
+      </c>
+      <c r="D188">
+        <v>2026</v>
+      </c>
+      <c r="E188" t="s">
+        <v>205</v>
+      </c>
+      <c r="F188" t="s">
+        <v>206</v>
+      </c>
+      <c r="G188" t="s">
+        <v>207</v>
+      </c>
+      <c r="H188">
+        <v>9</v>
+      </c>
+      <c r="I188">
+        <v>9</v>
+      </c>
+      <c r="M188" s="1">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="Q188" s="1">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>25013788</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="s">
+        <v>28</v>
+      </c>
+      <c r="D189">
+        <v>2026</v>
+      </c>
+      <c r="E189" t="s">
+        <v>205</v>
+      </c>
+      <c r="F189" t="s">
+        <v>206</v>
+      </c>
+      <c r="G189" t="s">
+        <v>207</v>
+      </c>
+      <c r="H189">
+        <v>8</v>
+      </c>
+      <c r="I189">
+        <v>9</v>
+      </c>
+      <c r="M189" s="1">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="Q189" s="1">
+        <f t="shared" si="5"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>25013740</v>
+      </c>
+      <c r="B190" t="s">
+        <v>201</v>
+      </c>
+      <c r="C190" t="s">
+        <v>28</v>
+      </c>
+      <c r="D190">
+        <v>2026</v>
+      </c>
+      <c r="E190" t="s">
+        <v>205</v>
+      </c>
+      <c r="F190" t="s">
+        <v>206</v>
+      </c>
+      <c r="G190" t="s">
+        <v>207</v>
+      </c>
+      <c r="H190">
+        <v>7.9499999999999993</v>
+      </c>
+      <c r="I190">
+        <v>9</v>
+      </c>
+      <c r="M190" s="1">
+        <f t="shared" si="4"/>
+        <v>8.4749999999999996</v>
+      </c>
+      <c r="Q190" s="1">
+        <f t="shared" si="5"/>
+        <v>8.4749999999999996</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>25013760</v>
+      </c>
+      <c r="B191" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D191">
+        <v>2026</v>
+      </c>
+      <c r="E191" t="s">
+        <v>205</v>
+      </c>
+      <c r="F191" t="s">
+        <v>206</v>
+      </c>
+      <c r="G191" t="s">
+        <v>207</v>
+      </c>
+      <c r="H191">
+        <v>8</v>
+      </c>
+      <c r="I191">
+        <v>9</v>
+      </c>
+      <c r="M191" s="1">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="Q191" s="1">
+        <f t="shared" si="5"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>25013770</v>
+      </c>
+      <c r="B192" t="s">
+        <v>159</v>
+      </c>
+      <c r="C192" t="s">
+        <v>27</v>
+      </c>
+      <c r="D192">
+        <v>2026</v>
+      </c>
+      <c r="E192" t="s">
+        <v>205</v>
+      </c>
+      <c r="F192" t="s">
+        <v>206</v>
+      </c>
+      <c r="G192" t="s">
+        <v>207</v>
+      </c>
+      <c r="H192">
+        <v>7.5</v>
+      </c>
+      <c r="I192">
+        <v>10</v>
+      </c>
+      <c r="M192" s="1">
+        <f t="shared" si="4"/>
+        <v>8.75</v>
+      </c>
+      <c r="Q192" s="1">
+        <f t="shared" si="5"/>
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>25013736</v>
+      </c>
+      <c r="B193" t="s">
+        <v>202</v>
+      </c>
+      <c r="C193" t="s">
+        <v>27</v>
+      </c>
+      <c r="D193">
+        <v>2026</v>
+      </c>
+      <c r="E193" t="s">
+        <v>205</v>
+      </c>
+      <c r="F193" t="s">
+        <v>206</v>
+      </c>
+      <c r="G193" t="s">
+        <v>207</v>
+      </c>
+      <c r="H193">
+        <v>9.5</v>
+      </c>
+      <c r="I193">
+        <v>9</v>
+      </c>
+      <c r="M193" s="1">
+        <f t="shared" si="4"/>
+        <v>9.25</v>
+      </c>
+      <c r="Q193" s="1">
+        <f t="shared" si="5"/>
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>25013695</v>
+      </c>
+      <c r="B194" t="s">
+        <v>161</v>
+      </c>
+      <c r="C194" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194">
+        <v>2026</v>
+      </c>
+      <c r="E194" t="s">
+        <v>205</v>
+      </c>
+      <c r="F194" t="s">
+        <v>206</v>
+      </c>
+      <c r="G194" t="s">
+        <v>207</v>
+      </c>
+      <c r="H194">
+        <v>7.9999999999999991</v>
+      </c>
+      <c r="I194">
+        <v>9</v>
+      </c>
+      <c r="M194" s="1">
+        <f t="shared" si="4"/>
+        <v>8.5</v>
+      </c>
+      <c r="Q194" s="1">
+        <f t="shared" si="5"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>24032904</v>
+      </c>
+      <c r="B195" t="s">
+        <v>203</v>
+      </c>
+      <c r="C195" t="s">
+        <v>27</v>
+      </c>
+      <c r="D195">
+        <v>2026</v>
+      </c>
+      <c r="E195" t="s">
+        <v>205</v>
+      </c>
+      <c r="F195" t="s">
+        <v>206</v>
+      </c>
+      <c r="G195" t="s">
+        <v>207</v>
+      </c>
+      <c r="H195">
+        <v>5</v>
+      </c>
+      <c r="I195">
+        <v>5</v>
+      </c>
+      <c r="M195" s="1">
+        <f t="shared" ref="M195:M238" si="6">AVERAGE(H195:L195)</f>
+        <v>5</v>
+      </c>
+      <c r="Q195" s="1">
+        <f t="shared" ref="Q195:Q238" si="7">MAX(M195,O195,P195)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>24033514</v>
+      </c>
+      <c r="B196" t="s">
+        <v>204</v>
+      </c>
+      <c r="C196" t="s">
+        <v>27</v>
+      </c>
+      <c r="D196">
+        <v>2026</v>
+      </c>
+      <c r="E196" t="s">
+        <v>205</v>
+      </c>
+      <c r="F196" t="s">
+        <v>206</v>
+      </c>
+      <c r="G196" t="s">
+        <v>207</v>
+      </c>
+      <c r="H196">
+        <v>7</v>
+      </c>
+      <c r="I196">
+        <v>5</v>
+      </c>
+      <c r="M196" s="1">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="Q196" s="1">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>25011687</v>
+      </c>
+      <c r="B197" t="s">
+        <v>198</v>
+      </c>
+      <c r="C197" t="s">
+        <v>28</v>
+      </c>
+      <c r="D197">
+        <v>2026</v>
+      </c>
+      <c r="E197" t="s">
+        <v>205</v>
+      </c>
+      <c r="F197" t="s">
+        <v>157</v>
+      </c>
+      <c r="G197" t="s">
+        <v>207</v>
+      </c>
+      <c r="H197">
+        <v>9.9999999999999982</v>
+      </c>
+      <c r="I197">
+        <v>10.02</v>
+      </c>
+      <c r="M197" s="1">
+        <f t="shared" si="6"/>
+        <v>10.009999999999998</v>
+      </c>
+      <c r="Q197" s="1">
+        <f t="shared" si="7"/>
+        <v>10.009999999999998</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>25013735</v>
+      </c>
+      <c r="B198" t="s">
+        <v>199</v>
+      </c>
+      <c r="C198" t="s">
+        <v>27</v>
+      </c>
+      <c r="D198">
+        <v>2026</v>
+      </c>
+      <c r="E198" t="s">
+        <v>205</v>
+      </c>
+      <c r="F198" t="s">
+        <v>157</v>
+      </c>
+      <c r="G198" t="s">
+        <v>207</v>
+      </c>
+      <c r="H198">
+        <v>8.5</v>
+      </c>
+      <c r="I198">
+        <v>8.0381818181818172</v>
+      </c>
+      <c r="M198" s="1">
+        <f t="shared" si="6"/>
+        <v>8.2690909090909095</v>
+      </c>
+      <c r="Q198" s="1">
+        <f t="shared" si="7"/>
+        <v>8.2690909090909095</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>25013035</v>
+      </c>
+      <c r="B199" t="s">
+        <v>200</v>
+      </c>
+      <c r="C199" t="s">
+        <v>27</v>
+      </c>
+      <c r="D199">
+        <v>2026</v>
+      </c>
+      <c r="E199" t="s">
+        <v>205</v>
+      </c>
+      <c r="F199" t="s">
+        <v>157</v>
+      </c>
+      <c r="G199" t="s">
+        <v>207</v>
+      </c>
+      <c r="H199">
+        <v>10</v>
+      </c>
+      <c r="I199">
+        <v>10.018181818181818</v>
+      </c>
+      <c r="M199" s="1">
+        <f t="shared" si="6"/>
+        <v>10.009090909090908</v>
+      </c>
+      <c r="Q199" s="1">
+        <f t="shared" si="7"/>
+        <v>10.009090909090908</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>25013788</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="s">
+        <v>28</v>
+      </c>
+      <c r="D200">
+        <v>2026</v>
+      </c>
+      <c r="E200" t="s">
+        <v>205</v>
+      </c>
+      <c r="F200" t="s">
+        <v>157</v>
+      </c>
+      <c r="G200" t="s">
+        <v>207</v>
+      </c>
+      <c r="H200">
+        <v>9</v>
+      </c>
+      <c r="I200">
+        <v>10</v>
+      </c>
+      <c r="M200" s="1">
+        <f t="shared" si="6"/>
+        <v>9.5</v>
+      </c>
+      <c r="Q200" s="1">
+        <f t="shared" si="7"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>25013740</v>
+      </c>
+      <c r="B201" t="s">
+        <v>201</v>
+      </c>
+      <c r="C201" t="s">
+        <v>28</v>
+      </c>
+      <c r="D201">
+        <v>2026</v>
+      </c>
+      <c r="E201" t="s">
+        <v>205</v>
+      </c>
+      <c r="F201" t="s">
+        <v>157</v>
+      </c>
+      <c r="G201" t="s">
+        <v>207</v>
+      </c>
+      <c r="H201">
+        <v>8</v>
+      </c>
+      <c r="I201">
+        <v>9.4563636363636352</v>
+      </c>
+      <c r="M201" s="1">
+        <f t="shared" si="6"/>
+        <v>8.7281818181818167</v>
+      </c>
+      <c r="Q201" s="1">
+        <f t="shared" si="7"/>
+        <v>8.7281818181818167</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>25013760</v>
+      </c>
+      <c r="B202" t="s">
+        <v>17</v>
+      </c>
+      <c r="C202" t="s">
+        <v>27</v>
+      </c>
+      <c r="D202">
+        <v>2026</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+      <c r="F202" t="s">
+        <v>157</v>
+      </c>
+      <c r="G202" t="s">
+        <v>207</v>
+      </c>
+      <c r="H202">
+        <v>9.4999999999999982</v>
+      </c>
+      <c r="I202">
+        <v>9.52</v>
+      </c>
+      <c r="M202" s="1">
+        <f t="shared" si="6"/>
+        <v>9.509999999999998</v>
+      </c>
+      <c r="Q202" s="1">
+        <f t="shared" si="7"/>
+        <v>9.509999999999998</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>25013770</v>
+      </c>
+      <c r="B203" t="s">
+        <v>159</v>
+      </c>
+      <c r="C203" t="s">
+        <v>27</v>
+      </c>
+      <c r="D203">
+        <v>2026</v>
+      </c>
+      <c r="E203" t="s">
+        <v>205</v>
+      </c>
+      <c r="F203" t="s">
+        <v>157</v>
+      </c>
+      <c r="G203" t="s">
+        <v>207</v>
+      </c>
+      <c r="H203">
+        <v>9</v>
+      </c>
+      <c r="I203">
+        <v>10</v>
+      </c>
+      <c r="M203" s="1">
+        <f t="shared" si="6"/>
+        <v>9.5</v>
+      </c>
+      <c r="Q203" s="1">
+        <f t="shared" si="7"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>25013736</v>
+      </c>
+      <c r="B204" t="s">
+        <v>202</v>
+      </c>
+      <c r="C204" t="s">
+        <v>27</v>
+      </c>
+      <c r="D204">
+        <v>2026</v>
+      </c>
+      <c r="E204" t="s">
+        <v>205</v>
+      </c>
+      <c r="F204" t="s">
+        <v>157</v>
+      </c>
+      <c r="G204" t="s">
+        <v>207</v>
+      </c>
+      <c r="H204">
+        <v>9.4999999999999982</v>
+      </c>
+      <c r="I204">
+        <v>10</v>
+      </c>
+      <c r="M204" s="1">
+        <f t="shared" si="6"/>
+        <v>9.75</v>
+      </c>
+      <c r="Q204" s="1">
+        <f t="shared" si="7"/>
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>25013695</v>
+      </c>
+      <c r="B205" t="s">
+        <v>161</v>
+      </c>
+      <c r="C205" t="s">
+        <v>27</v>
+      </c>
+      <c r="D205">
+        <v>2026</v>
+      </c>
+      <c r="E205" t="s">
+        <v>205</v>
+      </c>
+      <c r="F205" t="s">
+        <v>157</v>
+      </c>
+      <c r="G205" t="s">
+        <v>207</v>
+      </c>
+      <c r="H205">
+        <v>10</v>
+      </c>
+      <c r="I205">
+        <v>10.038181818181817</v>
+      </c>
+      <c r="M205" s="1">
+        <f t="shared" si="6"/>
+        <v>10.019090909090909</v>
+      </c>
+      <c r="Q205" s="1">
+        <f t="shared" si="7"/>
+        <v>10.019090909090909</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>24032904</v>
+      </c>
+      <c r="B206" t="s">
+        <v>203</v>
+      </c>
+      <c r="C206" t="s">
+        <v>27</v>
+      </c>
+      <c r="D206">
+        <v>2026</v>
+      </c>
+      <c r="E206" t="s">
+        <v>205</v>
+      </c>
+      <c r="F206" t="s">
+        <v>157</v>
+      </c>
+      <c r="G206" t="s">
+        <v>207</v>
+      </c>
+      <c r="H206">
+        <v>7</v>
+      </c>
+      <c r="I206">
+        <v>5.963636363636363</v>
+      </c>
+      <c r="M206" s="1">
+        <f t="shared" si="6"/>
+        <v>6.4818181818181815</v>
+      </c>
+      <c r="Q206" s="1">
+        <f t="shared" si="7"/>
+        <v>6.4818181818181815</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>24033514</v>
+      </c>
+      <c r="B207" t="s">
+        <v>204</v>
+      </c>
+      <c r="C207" t="s">
+        <v>27</v>
+      </c>
+      <c r="D207">
+        <v>2026</v>
+      </c>
+      <c r="E207" t="s">
+        <v>205</v>
+      </c>
+      <c r="F207" t="s">
+        <v>157</v>
+      </c>
+      <c r="G207" t="s">
+        <v>207</v>
+      </c>
+      <c r="H207">
+        <v>7</v>
+      </c>
+      <c r="I207">
+        <v>4.9909090909090912</v>
+      </c>
+      <c r="M207" s="1">
+        <f t="shared" si="6"/>
+        <v>5.995454545454546</v>
+      </c>
+      <c r="Q207" s="1">
+        <f t="shared" si="7"/>
+        <v>5.995454545454546</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>24033504</v>
+      </c>
+      <c r="B208" t="s">
+        <v>208</v>
+      </c>
+      <c r="C208" t="s">
+        <v>27</v>
+      </c>
+      <c r="D208">
+        <v>2026</v>
+      </c>
+      <c r="E208" t="s">
+        <v>205</v>
+      </c>
+      <c r="F208" t="s">
+        <v>239</v>
+      </c>
+      <c r="G208" t="s">
+        <v>129</v>
+      </c>
+      <c r="H208">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="I208">
+        <v>10</v>
+      </c>
+      <c r="M208" s="1">
+        <f t="shared" si="6"/>
+        <v>9.23</v>
+      </c>
+      <c r="Q208" s="1">
+        <f t="shared" si="7"/>
+        <v>9.23</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>24033162</v>
+      </c>
+      <c r="B209" t="s">
+        <v>209</v>
+      </c>
+      <c r="C209" t="s">
+        <v>27</v>
+      </c>
+      <c r="D209">
+        <v>2026</v>
+      </c>
+      <c r="E209" t="s">
+        <v>205</v>
+      </c>
+      <c r="F209" t="s">
+        <v>239</v>
+      </c>
+      <c r="G209" t="s">
+        <v>129</v>
+      </c>
+      <c r="H209">
+        <v>6.5142857142857142</v>
+      </c>
+      <c r="I209">
+        <v>9.4999999999999982</v>
+      </c>
+      <c r="M209" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0071428571428562</v>
+      </c>
+      <c r="Q209" s="1">
+        <f t="shared" si="7"/>
+        <v>8.0071428571428562</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>24033311</v>
+      </c>
+      <c r="B210" t="s">
+        <v>210</v>
+      </c>
+      <c r="C210" t="s">
+        <v>28</v>
+      </c>
+      <c r="D210">
+        <v>2026</v>
+      </c>
+      <c r="E210" t="s">
+        <v>205</v>
+      </c>
+      <c r="F210" t="s">
+        <v>239</v>
+      </c>
+      <c r="G210" t="s">
+        <v>129</v>
+      </c>
+      <c r="H210">
+        <v>10</v>
+      </c>
+      <c r="I210">
+        <v>10</v>
+      </c>
+      <c r="M210" s="1">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="Q210" s="1">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>24032902</v>
+      </c>
+      <c r="B211" t="s">
+        <v>211</v>
+      </c>
+      <c r="C211" t="s">
+        <v>27</v>
+      </c>
+      <c r="D211">
+        <v>2026</v>
+      </c>
+      <c r="E211" t="s">
+        <v>205</v>
+      </c>
+      <c r="F211" t="s">
+        <v>239</v>
+      </c>
+      <c r="G211" t="s">
+        <v>129</v>
+      </c>
+      <c r="H211">
+        <v>7.4728571428571424</v>
+      </c>
+      <c r="I211">
+        <v>8.6666666666666679</v>
+      </c>
+      <c r="M211" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0697619047619042</v>
+      </c>
+      <c r="Q211" s="1">
+        <f t="shared" si="7"/>
+        <v>8.0697619047619042</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>24033017</v>
+      </c>
+      <c r="B212" t="s">
+        <v>212</v>
+      </c>
+      <c r="C212" t="s">
+        <v>27</v>
+      </c>
+      <c r="D212">
+        <v>2026</v>
+      </c>
+      <c r="E212" t="s">
+        <v>205</v>
+      </c>
+      <c r="F212" t="s">
+        <v>239</v>
+      </c>
+      <c r="G212" t="s">
+        <v>129</v>
+      </c>
+      <c r="H212">
+        <v>7.0442857142857136</v>
+      </c>
+      <c r="I212">
+        <v>10</v>
+      </c>
+      <c r="M212" s="1">
+        <f t="shared" si="6"/>
+        <v>8.5221428571428568</v>
+      </c>
+      <c r="Q212" s="1">
+        <f t="shared" si="7"/>
+        <v>8.5221428571428568</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>24032932</v>
+      </c>
+      <c r="B213" t="s">
+        <v>213</v>
+      </c>
+      <c r="C213" t="s">
+        <v>28</v>
+      </c>
+      <c r="D213">
+        <v>2026</v>
+      </c>
+      <c r="E213" t="s">
+        <v>205</v>
+      </c>
+      <c r="F213" t="s">
+        <v>239</v>
+      </c>
+      <c r="G213" t="s">
+        <v>129</v>
+      </c>
+      <c r="H213">
+        <v>10.040000000000001</v>
+      </c>
+      <c r="I213">
+        <v>10</v>
+      </c>
+      <c r="M213" s="1">
+        <f t="shared" si="6"/>
+        <v>10.02</v>
+      </c>
+      <c r="Q213" s="1">
+        <f t="shared" si="7"/>
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>24033500</v>
+      </c>
+      <c r="B214" t="s">
+        <v>214</v>
+      </c>
+      <c r="C214" t="s">
+        <v>27</v>
+      </c>
+      <c r="D214">
+        <v>2026</v>
+      </c>
+      <c r="E214" t="s">
+        <v>205</v>
+      </c>
+      <c r="F214" t="s">
+        <v>239</v>
+      </c>
+      <c r="G214" t="s">
+        <v>129</v>
+      </c>
+      <c r="H214">
+        <v>7.9785714285714286</v>
+      </c>
+      <c r="I214">
+        <v>6.5</v>
+      </c>
+      <c r="M214" s="1">
+        <f t="shared" si="6"/>
+        <v>7.2392857142857139</v>
+      </c>
+      <c r="Q214" s="1">
+        <f t="shared" si="7"/>
+        <v>7.2392857142857139</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>24033149</v>
+      </c>
+      <c r="B215" t="s">
+        <v>215</v>
+      </c>
+      <c r="C215" t="s">
+        <v>28</v>
+      </c>
+      <c r="D215">
+        <v>2026</v>
+      </c>
+      <c r="E215" t="s">
+        <v>205</v>
+      </c>
+      <c r="F215" t="s">
+        <v>239</v>
+      </c>
+      <c r="G215" t="s">
+        <v>129</v>
+      </c>
+      <c r="H215">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="I215">
+        <v>10</v>
+      </c>
+      <c r="M215" s="1">
+        <f t="shared" si="6"/>
+        <v>9.77</v>
+      </c>
+      <c r="Q215" s="1">
+        <f t="shared" si="7"/>
+        <v>9.77</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>24033109</v>
+      </c>
+      <c r="B216" t="s">
+        <v>216</v>
+      </c>
+      <c r="C216" t="s">
+        <v>28</v>
+      </c>
+      <c r="D216">
+        <v>2026</v>
+      </c>
+      <c r="E216" t="s">
+        <v>205</v>
+      </c>
+      <c r="F216" t="s">
+        <v>239</v>
+      </c>
+      <c r="G216" t="s">
+        <v>129</v>
+      </c>
+      <c r="H216">
+        <v>9.5</v>
+      </c>
+      <c r="I216">
+        <v>10</v>
+      </c>
+      <c r="M216" s="1">
+        <f t="shared" si="6"/>
+        <v>9.75</v>
+      </c>
+      <c r="Q216" s="1">
+        <f t="shared" si="7"/>
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>24033317</v>
+      </c>
+      <c r="B217" t="s">
+        <v>217</v>
+      </c>
+      <c r="C217" t="s">
+        <v>27</v>
+      </c>
+      <c r="D217">
+        <v>2026</v>
+      </c>
+      <c r="E217" t="s">
+        <v>205</v>
+      </c>
+      <c r="F217" t="s">
+        <v>239</v>
+      </c>
+      <c r="G217" t="s">
+        <v>129</v>
+      </c>
+      <c r="H217">
+        <v>10</v>
+      </c>
+      <c r="I217">
+        <v>10</v>
+      </c>
+      <c r="M217" s="1">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="Q217" s="1">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>24033516</v>
+      </c>
+      <c r="B218" t="s">
+        <v>218</v>
+      </c>
+      <c r="C218" t="s">
+        <v>27</v>
+      </c>
+      <c r="D218">
+        <v>2026</v>
+      </c>
+      <c r="E218" t="s">
+        <v>205</v>
+      </c>
+      <c r="F218" t="s">
+        <v>239</v>
+      </c>
+      <c r="G218" t="s">
+        <v>129</v>
+      </c>
+      <c r="H218">
+        <v>8.52</v>
+      </c>
+      <c r="I218">
+        <v>7.5333333333333341</v>
+      </c>
+      <c r="M218" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0266666666666673</v>
+      </c>
+      <c r="Q218" s="1">
+        <f t="shared" si="7"/>
+        <v>8.0266666666666673</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>24033592</v>
+      </c>
+      <c r="B219" t="s">
+        <v>219</v>
+      </c>
+      <c r="C219" t="s">
+        <v>28</v>
+      </c>
+      <c r="D219">
+        <v>2026</v>
+      </c>
+      <c r="E219" t="s">
+        <v>205</v>
+      </c>
+      <c r="F219" t="s">
+        <v>239</v>
+      </c>
+      <c r="G219" t="s">
+        <v>129</v>
+      </c>
+      <c r="H219">
+        <v>10</v>
+      </c>
+      <c r="I219">
+        <v>8.9666666666666686</v>
+      </c>
+      <c r="M219" s="1">
+        <f t="shared" si="6"/>
+        <v>9.4833333333333343</v>
+      </c>
+      <c r="Q219" s="1">
+        <f t="shared" si="7"/>
+        <v>9.4833333333333343</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>24033301</v>
+      </c>
+      <c r="B220" t="s">
+        <v>220</v>
+      </c>
+      <c r="C220" t="s">
+        <v>27</v>
+      </c>
+      <c r="D220">
+        <v>2026</v>
+      </c>
+      <c r="E220" t="s">
+        <v>205</v>
+      </c>
+      <c r="F220" t="s">
+        <v>239</v>
+      </c>
+      <c r="G220" t="s">
+        <v>129</v>
+      </c>
+      <c r="H220">
+        <v>8.5285714285714285</v>
+      </c>
+      <c r="I220">
+        <v>7.5333333333333341</v>
+      </c>
+      <c r="M220" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0309523809523817</v>
+      </c>
+      <c r="Q220" s="1">
+        <f t="shared" si="7"/>
+        <v>8.0309523809523817</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>24033416</v>
+      </c>
+      <c r="B221" t="s">
+        <v>221</v>
+      </c>
+      <c r="C221" t="s">
+        <v>27</v>
+      </c>
+      <c r="D221">
+        <v>2026</v>
+      </c>
+      <c r="E221" t="s">
+        <v>205</v>
+      </c>
+      <c r="F221" t="s">
+        <v>239</v>
+      </c>
+      <c r="G221" t="s">
+        <v>129</v>
+      </c>
+      <c r="H221">
+        <v>10</v>
+      </c>
+      <c r="I221">
+        <v>8.9666666666666686</v>
+      </c>
+      <c r="M221" s="1">
+        <f t="shared" si="6"/>
+        <v>9.4833333333333343</v>
+      </c>
+      <c r="Q221" s="1">
+        <f t="shared" si="7"/>
+        <v>9.4833333333333343</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>24033349</v>
+      </c>
+      <c r="B222" t="s">
+        <v>222</v>
+      </c>
+      <c r="C222" t="s">
+        <v>27</v>
+      </c>
+      <c r="D222">
+        <v>2026</v>
+      </c>
+      <c r="E222" t="s">
+        <v>205</v>
+      </c>
+      <c r="F222" t="s">
+        <v>239</v>
+      </c>
+      <c r="G222" t="s">
+        <v>129</v>
+      </c>
+      <c r="H222">
+        <v>10.014285714285714</v>
+      </c>
+      <c r="I222">
+        <v>6</v>
+      </c>
+      <c r="M222" s="1">
+        <f t="shared" si="6"/>
+        <v>8.0071428571428562</v>
+      </c>
+      <c r="Q222" s="1">
+        <f t="shared" si="7"/>
+        <v>8.0071428571428562</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>24033443</v>
+      </c>
+      <c r="B223" t="s">
+        <v>223</v>
+      </c>
+      <c r="C223" t="s">
+        <v>27</v>
+      </c>
+      <c r="D223">
+        <v>2026</v>
+      </c>
+      <c r="E223" t="s">
+        <v>205</v>
+      </c>
+      <c r="F223" t="s">
+        <v>239</v>
+      </c>
+      <c r="G223" t="s">
+        <v>129</v>
+      </c>
+      <c r="H223">
+        <v>7.0099999999999989</v>
+      </c>
+      <c r="I223">
+        <v>10</v>
+      </c>
+      <c r="M223" s="1">
+        <f t="shared" si="6"/>
+        <v>8.504999999999999</v>
+      </c>
+      <c r="Q223" s="1">
+        <f t="shared" si="7"/>
+        <v>8.504999999999999</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>24033137</v>
+      </c>
+      <c r="B224" t="s">
+        <v>224</v>
+      </c>
+      <c r="C224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D224">
+        <v>2026</v>
+      </c>
+      <c r="E224" t="s">
+        <v>205</v>
+      </c>
+      <c r="F224" t="s">
+        <v>239</v>
+      </c>
+      <c r="G224" t="s">
+        <v>129</v>
+      </c>
+      <c r="H224">
+        <v>9.9542857142857155</v>
+      </c>
+      <c r="I224">
+        <v>10</v>
+      </c>
+      <c r="M224" s="1">
+        <f t="shared" si="6"/>
+        <v>9.9771428571428586</v>
+      </c>
+      <c r="Q224" s="1">
+        <f t="shared" si="7"/>
+        <v>9.9771428571428586</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>24033554</v>
+      </c>
+      <c r="B225" t="s">
+        <v>225</v>
+      </c>
+      <c r="C225" t="s">
+        <v>28</v>
+      </c>
+      <c r="D225">
+        <v>2026</v>
+      </c>
+      <c r="E225" t="s">
+        <v>205</v>
+      </c>
+      <c r="F225" t="s">
+        <v>239</v>
+      </c>
+      <c r="G225" t="s">
+        <v>129</v>
+      </c>
+      <c r="H225">
+        <v>8.024285714285714</v>
+      </c>
+      <c r="I225">
+        <v>8.4666666666666668</v>
+      </c>
+      <c r="M225" s="1">
+        <f t="shared" si="6"/>
+        <v>8.2454761904761895</v>
+      </c>
+      <c r="Q225" s="1">
+        <f t="shared" si="7"/>
+        <v>8.2454761904761895</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>24032921</v>
+      </c>
+      <c r="B226" t="s">
+        <v>226</v>
+      </c>
+      <c r="C226" t="s">
+        <v>27</v>
+      </c>
+      <c r="D226">
+        <v>2026</v>
+      </c>
+      <c r="E226" t="s">
+        <v>205</v>
+      </c>
+      <c r="F226" t="s">
+        <v>239</v>
+      </c>
+      <c r="G226" t="s">
+        <v>129</v>
+      </c>
+      <c r="H226">
+        <v>10</v>
+      </c>
+      <c r="I226">
+        <v>10</v>
+      </c>
+      <c r="M226" s="1">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="Q226" s="1">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>24033221</v>
+      </c>
+      <c r="B227" t="s">
+        <v>227</v>
+      </c>
+      <c r="C227" t="s">
+        <v>28</v>
+      </c>
+      <c r="D227">
+        <v>2026</v>
+      </c>
+      <c r="E227" t="s">
+        <v>205</v>
+      </c>
+      <c r="F227" t="s">
+        <v>239</v>
+      </c>
+      <c r="G227" t="s">
+        <v>129</v>
+      </c>
+      <c r="H227">
+        <v>6.4828571428571431</v>
+      </c>
+      <c r="I227">
+        <v>8.9666666666666686</v>
+      </c>
+      <c r="M227" s="1">
+        <f t="shared" si="6"/>
+        <v>7.7247619047619054</v>
+      </c>
+      <c r="Q227" s="1">
+        <f t="shared" si="7"/>
+        <v>7.7247619047619054</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>24033401</v>
+      </c>
+      <c r="B228" t="s">
+        <v>228</v>
+      </c>
+      <c r="C228" t="s">
+        <v>28</v>
+      </c>
+      <c r="D228">
+        <v>2026</v>
+      </c>
+      <c r="E228" t="s">
+        <v>205</v>
+      </c>
+      <c r="F228" t="s">
+        <v>239</v>
+      </c>
+      <c r="G228" t="s">
+        <v>129</v>
+      </c>
+      <c r="H228">
+        <v>9.9571428571428573</v>
+      </c>
+      <c r="I228">
+        <v>4</v>
+      </c>
+      <c r="M228" s="1">
+        <f t="shared" si="6"/>
+        <v>6.9785714285714286</v>
+      </c>
+      <c r="Q228" s="1">
+        <f t="shared" si="7"/>
+        <v>6.9785714285714286</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>24032978</v>
+      </c>
+      <c r="B229" t="s">
+        <v>229</v>
+      </c>
+      <c r="C229" t="s">
+        <v>28</v>
+      </c>
+      <c r="D229">
+        <v>2026</v>
+      </c>
+      <c r="E229" t="s">
+        <v>205</v>
+      </c>
+      <c r="F229" t="s">
+        <v>239</v>
+      </c>
+      <c r="G229" t="s">
+        <v>129</v>
+      </c>
+      <c r="H229">
+        <v>6.4971428571428573</v>
+      </c>
+      <c r="I229">
+        <v>8.5</v>
+      </c>
+      <c r="M229" s="1">
+        <f t="shared" si="6"/>
+        <v>7.4985714285714291</v>
+      </c>
+      <c r="Q229" s="1">
+        <f t="shared" si="7"/>
+        <v>7.4985714285714291</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>24032960</v>
+      </c>
+      <c r="B230" t="s">
+        <v>230</v>
+      </c>
+      <c r="C230" t="s">
+        <v>28</v>
+      </c>
+      <c r="D230">
+        <v>2026</v>
+      </c>
+      <c r="E230" t="s">
+        <v>205</v>
+      </c>
+      <c r="F230" t="s">
+        <v>239</v>
+      </c>
+      <c r="G230" t="s">
+        <v>129</v>
+      </c>
+      <c r="H230">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="I230">
+        <v>10</v>
+      </c>
+      <c r="M230" s="1">
+        <f t="shared" si="6"/>
+        <v>10.02</v>
+      </c>
+      <c r="Q230" s="1">
+        <f t="shared" si="7"/>
+        <v>10.02</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>24033013</v>
+      </c>
+      <c r="B231" t="s">
+        <v>231</v>
+      </c>
+      <c r="C231" t="s">
+        <v>27</v>
+      </c>
+      <c r="D231">
+        <v>2026</v>
+      </c>
+      <c r="E231" t="s">
+        <v>205</v>
+      </c>
+      <c r="F231" t="s">
+        <v>239</v>
+      </c>
+      <c r="G231" t="s">
+        <v>129</v>
+      </c>
+      <c r="H231">
+        <v>10.014285714285714</v>
+      </c>
+      <c r="I231">
+        <v>10</v>
+      </c>
+      <c r="M231" s="1">
+        <f t="shared" si="6"/>
+        <v>10.007142857142856</v>
+      </c>
+      <c r="Q231" s="1">
+        <f t="shared" si="7"/>
+        <v>10.007142857142856</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>24033155</v>
+      </c>
+      <c r="B232" t="s">
+        <v>232</v>
+      </c>
+      <c r="C232" t="s">
+        <v>27</v>
+      </c>
+      <c r="D232">
+        <v>2026</v>
+      </c>
+      <c r="E232" t="s">
+        <v>205</v>
+      </c>
+      <c r="F232" t="s">
+        <v>239</v>
+      </c>
+      <c r="G232" t="s">
+        <v>129</v>
+      </c>
+      <c r="H232">
+        <v>7.0457142857142854</v>
+      </c>
+      <c r="I232">
+        <v>7.5333333333333341</v>
+      </c>
+      <c r="M232" s="1">
+        <f t="shared" si="6"/>
+        <v>7.2895238095238097</v>
+      </c>
+      <c r="Q232" s="1">
+        <f t="shared" si="7"/>
+        <v>7.2895238095238097</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>24033537</v>
+      </c>
+      <c r="B233" t="s">
+        <v>233</v>
+      </c>
+      <c r="C233" t="s">
+        <v>27</v>
+      </c>
+      <c r="D233">
+        <v>2026</v>
+      </c>
+      <c r="E233" t="s">
+        <v>205</v>
+      </c>
+      <c r="F233" t="s">
+        <v>239</v>
+      </c>
+      <c r="G233" t="s">
+        <v>129</v>
+      </c>
+      <c r="H233">
+        <v>8.0028571428571418</v>
+      </c>
+      <c r="I233">
+        <v>8.9666666666666686</v>
+      </c>
+      <c r="M233" s="1">
+        <f t="shared" si="6"/>
+        <v>8.4847619047619052</v>
+      </c>
+      <c r="Q233" s="1">
+        <f t="shared" si="7"/>
+        <v>8.4847619047619052</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>24033538</v>
+      </c>
+      <c r="B234" t="s">
+        <v>234</v>
+      </c>
+      <c r="C234" t="s">
+        <v>27</v>
+      </c>
+      <c r="D234">
+        <v>2026</v>
+      </c>
+      <c r="E234" t="s">
+        <v>205</v>
+      </c>
+      <c r="F234" t="s">
+        <v>239</v>
+      </c>
+      <c r="G234" t="s">
+        <v>129</v>
+      </c>
+      <c r="H234">
+        <v>9.52</v>
+      </c>
+      <c r="I234">
+        <v>10</v>
+      </c>
+      <c r="M234" s="1">
+        <f t="shared" si="6"/>
+        <v>9.76</v>
+      </c>
+      <c r="Q234" s="1">
+        <f t="shared" si="7"/>
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>24033262</v>
+      </c>
+      <c r="B235" t="s">
+        <v>235</v>
+      </c>
+      <c r="C235" t="s">
+        <v>28</v>
+      </c>
+      <c r="D235">
+        <v>2026</v>
+      </c>
+      <c r="E235" t="s">
+        <v>205</v>
+      </c>
+      <c r="F235" t="s">
+        <v>239</v>
+      </c>
+      <c r="G235" t="s">
+        <v>129</v>
+      </c>
+      <c r="H235">
+        <v>9.51</v>
+      </c>
+      <c r="I235">
+        <v>10</v>
+      </c>
+      <c r="M235" s="1">
+        <f t="shared" si="6"/>
+        <v>9.754999999999999</v>
+      </c>
+      <c r="Q235" s="1">
+        <f t="shared" si="7"/>
+        <v>9.754999999999999</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>24033102</v>
+      </c>
+      <c r="B236" t="s">
+        <v>236</v>
+      </c>
+      <c r="C236" t="s">
+        <v>27</v>
+      </c>
+      <c r="D236">
+        <v>2026</v>
+      </c>
+      <c r="E236" t="s">
+        <v>205</v>
+      </c>
+      <c r="F236" t="s">
+        <v>239</v>
+      </c>
+      <c r="G236" t="s">
+        <v>129</v>
+      </c>
+      <c r="H236">
+        <v>6.4742857142857142</v>
+      </c>
+      <c r="I236">
+        <v>6.5333333333333332</v>
+      </c>
+      <c r="M236" s="1">
+        <f t="shared" si="6"/>
+        <v>6.5038095238095242</v>
+      </c>
+      <c r="Q236" s="1">
+        <f t="shared" si="7"/>
+        <v>6.5038095238095242</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>24033577</v>
+      </c>
+      <c r="B237" t="s">
+        <v>237</v>
+      </c>
+      <c r="C237" t="s">
+        <v>27</v>
+      </c>
+      <c r="D237">
+        <v>2026</v>
+      </c>
+      <c r="E237" t="s">
+        <v>205</v>
+      </c>
+      <c r="F237" t="s">
+        <v>239</v>
+      </c>
+      <c r="G237" t="s">
+        <v>129</v>
+      </c>
+      <c r="H237">
+        <v>9.5028571428571436</v>
+      </c>
+      <c r="I237">
+        <v>7.5333333333333341</v>
+      </c>
+      <c r="M237" s="1">
+        <f t="shared" si="6"/>
+        <v>8.5180952380952384</v>
+      </c>
+      <c r="Q237" s="1">
+        <f t="shared" si="7"/>
+        <v>8.5180952380952384</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>24033093</v>
+      </c>
+      <c r="B238" t="s">
+        <v>238</v>
+      </c>
+      <c r="C238" t="s">
+        <v>27</v>
+      </c>
+      <c r="D238">
+        <v>2026</v>
+      </c>
+      <c r="E238" t="s">
+        <v>205</v>
+      </c>
+      <c r="F238" t="s">
+        <v>239</v>
+      </c>
+      <c r="G238" t="s">
+        <v>129</v>
+      </c>
+      <c r="H238">
+        <v>9.5285714285714302</v>
+      </c>
+      <c r="I238">
+        <v>10</v>
+      </c>
+      <c r="M238" s="1">
+        <f t="shared" si="6"/>
+        <v>9.764285714285716</v>
+      </c>
+      <c r="Q238" s="1">
+        <f t="shared" si="7"/>
+        <v>9.764285714285716</v>
       </c>
     </row>
   </sheetData>
